--- a/backend/Rwanda/design-capital-{model}.xlsx
+++ b/backend/Rwanda/design-capital-{model}.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8954da175e61d5af/Escritorio/IIT/CC-WBT/backend/LPG testing/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8954da175e61d5af/Escritorio/IIT/CC-WBT/backend/{templates}/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="28" documentId="13_ncr:1_{E7EEBAEC-A995-406F-B1EA-27A046371A3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7EFB680D-0997-4CE1-A38F-AB0E77F3A992}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="13_ncr:1_{E7EEBAEC-A995-406F-B1EA-27A046371A3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57E91E27-747D-4DF9-8535-7A868DCDF9AA}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{BBCF56CD-8AD5-4002-91F7-ED7A4CE8CFDA}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{BBCF56CD-8AD5-4002-91F7-ED7A4CE8CFDA}"/>
   </bookViews>
   <sheets>
     <sheet name="Electricity &amp; E-Cooking" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="51">
   <si>
     <t>%</t>
   </si>
@@ -50,9 +50,6 @@
   </si>
   <si>
     <t>Amortization period</t>
-  </si>
-  <si>
-    <t>Baseline</t>
   </si>
   <si>
     <t>Annual debt needs</t>
@@ -410,47 +407,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="24">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="20">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -995,13 +952,13 @@
   <sheetData>
     <row r="1" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A1" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D1" s="8"/>
       <c r="E1" s="8"/>
@@ -1047,7 +1004,7 @@
     </row>
     <row r="2" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>0</v>
@@ -1099,7 +1056,7 @@
     </row>
     <row r="3" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A3" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>0</v>
@@ -1151,7 +1108,7 @@
     </row>
     <row r="4" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A4" s="22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>0</v>
@@ -1203,13 +1160,13 @@
     </row>
     <row r="5" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A5" s="22" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
@@ -1255,7 +1212,7 @@
     </row>
     <row r="6" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A6" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>0</v>
@@ -1307,7 +1264,7 @@
     </row>
     <row r="7" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>2</v>
@@ -1359,7 +1316,7 @@
     </row>
     <row r="8" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A8" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>2</v>
@@ -1411,7 +1368,7 @@
     </row>
     <row r="9" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A9" s="22" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>0</v>
@@ -1509,13 +1466,13 @@
     </row>
     <row r="11" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A11" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
@@ -1561,7 +1518,7 @@
     </row>
     <row r="12" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A12" s="22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>0</v>
@@ -1613,7 +1570,7 @@
     </row>
     <row r="13" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A13" s="14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>0</v>
@@ -1665,7 +1622,7 @@
     </row>
     <row r="14" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A14" s="22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>0</v>
@@ -1717,13 +1674,13 @@
     </row>
     <row r="15" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A15" s="22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D15" s="8"/>
       <c r="E15" s="8"/>
@@ -1769,7 +1726,7 @@
     </row>
     <row r="16" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A16" s="14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>0</v>
@@ -1821,7 +1778,7 @@
     </row>
     <row r="17" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A17" s="14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>2</v>
@@ -1873,7 +1830,7 @@
     </row>
     <row r="18" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A18" s="14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>2</v>
@@ -1925,7 +1882,7 @@
     </row>
     <row r="19" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A19" s="22" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>0</v>
@@ -2023,13 +1980,13 @@
     </row>
     <row r="21" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A21" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C21" s="21" t="s">
-        <v>4</v>
+      <c r="C21" s="21">
+        <v>2020</v>
       </c>
       <c r="D21" s="21">
         <v>2021</v>
@@ -2155,142 +2112,142 @@
     </row>
     <row r="22" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A22" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="S22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="T22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="U22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="X22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Z22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AB22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AC22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AD22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AN22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR22" s="16"/>
     </row>
     <row r="23" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A23" s="9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C23" s="18">
         <v>0</v>
@@ -2419,10 +2376,10 @@
     </row>
     <row r="24" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A24" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" s="4" t="s">
         <v>6</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>7</v>
       </c>
       <c r="C24" s="18">
         <v>0</v>
@@ -2597,13 +2554,13 @@
     </row>
     <row r="26" spans="1:44" s="3" customFormat="1" ht="16" x14ac:dyDescent="0.35">
       <c r="A26" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" s="12" t="s">
         <v>8</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>9</v>
       </c>
       <c r="D26" s="13"/>
       <c r="E26" s="13"/>
@@ -2649,10 +2606,10 @@
     </row>
     <row r="27" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A27" s="14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C27" s="15">
         <v>0</v>
@@ -2747,13 +2704,13 @@
     </row>
     <row r="29" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A29" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D29" s="8"/>
       <c r="E29" s="8"/>
@@ -2799,10 +2756,10 @@
     </row>
     <row r="30" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A30" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C30" s="18">
         <v>0</v>
@@ -2851,10 +2808,10 @@
     </row>
     <row r="31" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A31" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C31" s="18">
         <v>0</v>
@@ -2903,10 +2860,10 @@
     </row>
     <row r="32" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A32" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C32" s="18">
         <v>0</v>
@@ -2955,13 +2912,13 @@
     </row>
     <row r="34" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A34" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D34" s="8"/>
       <c r="E34" s="8"/>
@@ -3007,10 +2964,10 @@
     </row>
     <row r="35" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A35" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C35" s="18">
         <v>0</v>
@@ -3059,10 +3016,10 @@
     </row>
     <row r="36" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A36" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C36" s="18">
         <v>0</v>
@@ -3111,10 +3068,10 @@
     </row>
     <row r="37" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A37" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C37" s="18">
         <v>0</v>
@@ -3162,35 +3119,27 @@
       <c r="AR37" s="16"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A22:B22">
-    <cfRule type="cellIs" dxfId="23" priority="21" operator="equal">
+  <conditionalFormatting sqref="A22:AQ22">
+    <cfRule type="cellIs" dxfId="19" priority="1" operator="equal">
       <formula>"increase debt"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="22" priority="22" operator="equal">
+    <cfRule type="cellIs" dxfId="18" priority="2" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15:C15">
-    <cfRule type="cellIs" dxfId="21" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="17" priority="3" operator="equal">
       <formula>"increase debt"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="20" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="4" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5:AJ5">
-    <cfRule type="cellIs" dxfId="19" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="15" priority="5" operator="equal">
       <formula>"increase debt"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="18" priority="6" operator="equal">
-      <formula>"ok"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C22:AQ22">
-    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
-      <formula>"increase debt"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="6" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3210,13 +3159,13 @@
   <sheetData>
     <row r="1" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A1" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D1" s="8"/>
       <c r="E1" s="8"/>
@@ -3262,7 +3211,7 @@
     </row>
     <row r="2" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>0</v>
@@ -3314,7 +3263,7 @@
     </row>
     <row r="3" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A3" s="14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>0</v>
@@ -3366,7 +3315,7 @@
     </row>
     <row r="4" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A4" s="22" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>0</v>
@@ -3418,13 +3367,13 @@
     </row>
     <row r="5" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A5" s="22" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
@@ -3470,7 +3419,7 @@
     </row>
     <row r="6" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A6" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>0</v>
@@ -3522,7 +3471,7 @@
     </row>
     <row r="7" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>2</v>
@@ -3574,7 +3523,7 @@
     </row>
     <row r="8" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A8" s="14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>2</v>
@@ -3626,7 +3575,7 @@
     </row>
     <row r="9" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A9" s="22" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>0</v>
@@ -3724,13 +3673,13 @@
     </row>
     <row r="11" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A11" s="10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D11" s="8"/>
       <c r="E11" s="8"/>
@@ -3776,7 +3725,7 @@
     </row>
     <row r="12" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A12" s="22" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>0</v>
@@ -3828,7 +3777,7 @@
     </row>
     <row r="13" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A13" s="14" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>0</v>
@@ -3880,7 +3829,7 @@
     </row>
     <row r="14" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A14" s="22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>0</v>
@@ -3932,13 +3881,13 @@
     </row>
     <row r="15" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A15" s="22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B15" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D15" s="8"/>
       <c r="E15" s="8"/>
@@ -3984,7 +3933,7 @@
     </row>
     <row r="16" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A16" s="14" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>0</v>
@@ -4036,7 +3985,7 @@
     </row>
     <row r="17" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A17" s="14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>2</v>
@@ -4088,7 +4037,7 @@
     </row>
     <row r="18" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A18" s="14" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>2</v>
@@ -4140,7 +4089,7 @@
     </row>
     <row r="19" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A19" s="22" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>0</v>
@@ -4238,13 +4187,13 @@
     </row>
     <row r="21" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A21" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B21" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B21" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C21" s="21" t="s">
-        <v>4</v>
+      <c r="C21" s="21">
+        <v>2020</v>
       </c>
       <c r="D21" s="21">
         <v>2021</v>
@@ -4370,142 +4319,142 @@
     </row>
     <row r="22" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A22" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B22" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="S22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="T22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="U22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="X22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Z22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AB22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AC22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AD22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AN22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ22" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR22" s="16"/>
     </row>
     <row r="23" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A23" s="9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C23" s="18">
         <v>0</v>
@@ -4634,10 +4583,10 @@
     </row>
     <row r="24" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A24" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B24" s="4" t="s">
         <v>6</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>7</v>
       </c>
       <c r="C24" s="18">
         <v>0</v>
@@ -4812,13 +4761,13 @@
     </row>
     <row r="26" spans="1:44" s="3" customFormat="1" ht="16" x14ac:dyDescent="0.35">
       <c r="A26" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C26" s="12" t="s">
         <v>8</v>
-      </c>
-      <c r="B26" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>9</v>
       </c>
       <c r="D26" s="13"/>
       <c r="E26" s="13"/>
@@ -4864,10 +4813,10 @@
     </row>
     <row r="27" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A27" s="14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C27" s="15">
         <v>0</v>
@@ -4962,13 +4911,13 @@
     </row>
     <row r="29" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A29" s="10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B29" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C29" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D29" s="8"/>
       <c r="E29" s="8"/>
@@ -5014,10 +4963,10 @@
     </row>
     <row r="30" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A30" s="5" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C30" s="18">
         <v>0</v>
@@ -5066,10 +5015,10 @@
     </row>
     <row r="31" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A31" s="5" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C31" s="18">
         <v>0</v>
@@ -5118,10 +5067,10 @@
     </row>
     <row r="32" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A32" s="5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C32" s="18">
         <v>0</v>
@@ -5170,13 +5119,13 @@
     </row>
     <row r="34" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A34" s="10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C34" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D34" s="8"/>
       <c r="E34" s="8"/>
@@ -5222,10 +5171,10 @@
     </row>
     <row r="35" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A35" s="5" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C35" s="18">
         <v>0</v>
@@ -5274,10 +5223,10 @@
     </row>
     <row r="36" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A36" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C36" s="18">
         <v>0</v>
@@ -5326,10 +5275,10 @@
     </row>
     <row r="37" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A37" s="5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C37" s="18">
         <v>0</v>
@@ -5515,35 +5464,27 @@
       <c r="AR42" s="16"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A22">
-    <cfRule type="cellIs" dxfId="17" priority="7" operator="equal">
+  <conditionalFormatting sqref="A22:AQ22">
+    <cfRule type="cellIs" dxfId="13" priority="1" operator="equal">
       <formula>"increase debt"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="16" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="2" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B15:C15">
-    <cfRule type="cellIs" dxfId="15" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="11" priority="3" operator="equal">
       <formula>"increase debt"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="14" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="4" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B5:AJ5">
-    <cfRule type="cellIs" dxfId="13" priority="5" operator="equal">
+    <cfRule type="cellIs" dxfId="9" priority="5" operator="equal">
       <formula>"increase debt"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="12" priority="6" operator="equal">
-      <formula>"ok"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="B22:AQ22">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
-      <formula>"increase debt"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="6" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5563,13 +5504,13 @@
   <sheetData>
     <row r="1" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A1" s="10" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B1" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C1" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D1" s="8"/>
       <c r="E1" s="8"/>
@@ -5615,7 +5556,7 @@
     </row>
     <row r="2" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A2" s="22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>0</v>
@@ -5667,7 +5608,7 @@
     </row>
     <row r="3" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A3" s="14" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>0</v>
@@ -5719,7 +5660,7 @@
     </row>
     <row r="4" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A4" s="22" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>0</v>
@@ -5771,13 +5712,13 @@
     </row>
     <row r="5" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A5" s="22" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C5" s="20" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
@@ -5823,7 +5764,7 @@
     </row>
     <row r="6" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A6" s="14" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>0</v>
@@ -5979,7 +5920,7 @@
     </row>
     <row r="9" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A9" s="22" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>0</v>
@@ -6077,13 +6018,13 @@
     </row>
     <row r="11" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A11" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="B11" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="21" t="s">
-        <v>4</v>
+      <c r="C11" s="21">
+        <v>2020</v>
       </c>
       <c r="D11" s="21">
         <v>2021</v>
@@ -6209,142 +6150,142 @@
     </row>
     <row r="12" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A12" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B12" s="19" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="K12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="N12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Q12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="R12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="S12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="T12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="U12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="V12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="X12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Y12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="Z12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AA12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AB12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AC12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AD12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AE12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AF12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AH12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AJ12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AM12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AN12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AQ12" s="24" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AR12" s="16"/>
     </row>
     <row r="13" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A13" s="9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C13" s="18">
         <v>0</v>
@@ -6473,10 +6414,10 @@
     </row>
     <row r="14" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A14" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" s="4" t="s">
         <v>6</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>7</v>
       </c>
       <c r="C14" s="18">
         <v>0</v>
@@ -6651,13 +6592,13 @@
     </row>
     <row r="16" spans="1:44" ht="16" x14ac:dyDescent="0.35">
       <c r="A16" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="C16" s="12" t="s">
         <v>8</v>
-      </c>
-      <c r="B16" s="11" t="s">
-        <v>14</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>9</v>
       </c>
       <c r="D16" s="13"/>
       <c r="E16" s="13"/>
@@ -6703,10 +6644,10 @@
     </row>
     <row r="17" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A17" s="14" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C17" s="15">
         <v>0</v>
@@ -6801,13 +6742,13 @@
     </row>
     <row r="19" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A19" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D19" s="8"/>
       <c r="E19" s="8"/>
@@ -6853,10 +6794,10 @@
     </row>
     <row r="20" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A20" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C20" s="18">
         <v>0</v>
@@ -6905,10 +6846,10 @@
     </row>
     <row r="21" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A21" s="5" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C21" s="18">
         <v>0</v>
@@ -6957,10 +6898,10 @@
     </row>
     <row r="22" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A22" s="5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C22" s="18">
         <v>0</v>
@@ -7054,35 +6995,35 @@
       <c r="AR23" s="16"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B5:C5">
-    <cfRule type="cellIs" dxfId="11" priority="5" operator="equal">
+  <conditionalFormatting sqref="A12:AQ12">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="equal">
       <formula>"increase debt"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="2" operator="equal">
+      <formula>"ok"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B5:C5">
+    <cfRule type="cellIs" dxfId="5" priority="5" operator="equal">
+      <formula>"increase debt"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="D3:AJ3">
-    <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
       <formula>"increase debt"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D6:AJ6 A12:B12">
-    <cfRule type="cellIs" dxfId="7" priority="9" operator="equal">
+  <conditionalFormatting sqref="D6:AJ6">
+    <cfRule type="cellIs" dxfId="1" priority="9" operator="equal">
       <formula>"increase debt"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="10" operator="equal">
-      <formula>"ok"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C12:AQ12">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
-      <formula>"increase debt"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="10" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/backend/Rwanda/design-capital-{model}.xlsx
+++ b/backend/Rwanda/design-capital-{model}.xlsx
@@ -5,12 +5,12 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\agarr\OneDrive\Escritorio\IIT\CC-WBT\backend\{templates}\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/8954da175e61d5af/Escritorio/IIT/CC-WBT/backend/{templates}/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CAF04F80-47CE-41BE-8209-9827F5D06D2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="13_ncr:1_{CAF04F80-47CE-41BE-8209-9827F5D06D2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{289D7ADD-36D0-4591-A65E-9BC651F859A4}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{BBCF56CD-8AD5-4002-91F7-ED7A4CE8CFDA}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="2" xr2:uid="{BBCF56CD-8AD5-4002-91F7-ED7A4CE8CFDA}"/>
   </bookViews>
   <sheets>
     <sheet name="Electricity &amp; E-Cooking" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="31">
   <si>
     <t>%</t>
   </si>
@@ -129,6 +129,9 @@
   <si>
     <t xml:space="preserve">Debt </t>
   </si>
+  <si>
+    <t>Years realisation</t>
+  </si>
 </sst>
 </file>
 
@@ -215,7 +218,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -237,6 +240,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -282,7 +291,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -358,212 +367,15 @@
     <xf numFmtId="3" fontId="4" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="38">
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="18">
     <dxf>
       <font>
         <color rgb="FF006100"/>
@@ -1080,7 +892,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD3833E1-9C55-460E-A922-AEA15E5E66A2}">
   <sheetPr codeName="Hoja2"/>
-  <dimension ref="A1:AT120"/>
+  <dimension ref="A1:AT27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="46.54296875" customWidth="1"/>
@@ -1295,15 +1107,13 @@
       <c r="AR4" s="15"/>
     </row>
     <row r="5" spans="1:46" ht="16" x14ac:dyDescent="0.4">
-      <c r="A5" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>15</v>
-      </c>
+      <c r="A5" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="14"/>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
@@ -1347,14 +1157,14 @@
       <c r="AR5" s="15"/>
     </row>
     <row r="6" spans="1:46" ht="16" x14ac:dyDescent="0.4">
-      <c r="A6" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C6" s="17">
-        <v>0</v>
+      <c r="A6" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>15</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
@@ -1391,8 +1201,8 @@
       <c r="AJ6" s="16"/>
       <c r="AK6" s="16"/>
       <c r="AL6" s="15"/>
-      <c r="AM6" s="16"/>
-      <c r="AN6" s="16"/>
+      <c r="AM6" s="15"/>
+      <c r="AN6" s="15"/>
       <c r="AO6" s="15"/>
       <c r="AP6" s="15"/>
       <c r="AQ6" s="15"/>
@@ -1400,10 +1210,10 @@
     </row>
     <row r="7" spans="1:46" ht="16" x14ac:dyDescent="0.4">
       <c r="A7" s="13" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C7" s="17">
         <v>0</v>
@@ -1440,8 +1250,8 @@
       <c r="AG7" s="15"/>
       <c r="AH7" s="15"/>
       <c r="AI7" s="15"/>
-      <c r="AJ7" s="15"/>
-      <c r="AK7" s="15"/>
+      <c r="AJ7" s="16"/>
+      <c r="AK7" s="16"/>
       <c r="AL7" s="15"/>
       <c r="AM7" s="16"/>
       <c r="AN7" s="16"/>
@@ -1452,7 +1262,7 @@
     </row>
     <row r="8" spans="1:46" ht="16" x14ac:dyDescent="0.4">
       <c r="A8" s="13" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>2</v>
@@ -1503,9 +1313,15 @@
       <c r="AR8" s="15"/>
     </row>
     <row r="9" spans="1:46" ht="16" x14ac:dyDescent="0.4">
-      <c r="A9" s="8"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="21"/>
+      <c r="A9" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="17">
+        <v>0</v>
+      </c>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
       <c r="F9" s="8"/>
@@ -1549,887 +1365,887 @@
       <c r="AR9" s="15"/>
     </row>
     <row r="10" spans="1:46" ht="16" x14ac:dyDescent="0.4">
-      <c r="A10" s="24" t="s">
+      <c r="A10" s="8"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8"/>
+      <c r="Q10" s="8"/>
+      <c r="R10" s="8"/>
+      <c r="S10" s="15"/>
+      <c r="T10" s="15"/>
+      <c r="U10" s="15"/>
+      <c r="V10" s="15"/>
+      <c r="W10" s="15"/>
+      <c r="X10" s="15"/>
+      <c r="Y10" s="15"/>
+      <c r="Z10" s="15"/>
+      <c r="AA10" s="15"/>
+      <c r="AB10" s="15"/>
+      <c r="AC10" s="15"/>
+      <c r="AD10" s="15"/>
+      <c r="AE10" s="15"/>
+      <c r="AF10" s="15"/>
+      <c r="AG10" s="15"/>
+      <c r="AH10" s="15"/>
+      <c r="AI10" s="15"/>
+      <c r="AJ10" s="15"/>
+      <c r="AK10" s="15"/>
+      <c r="AL10" s="15"/>
+      <c r="AM10" s="16"/>
+      <c r="AN10" s="16"/>
+      <c r="AO10" s="15"/>
+      <c r="AP10" s="15"/>
+      <c r="AQ10" s="15"/>
+      <c r="AR10" s="15"/>
+    </row>
+    <row r="11" spans="1:46" ht="16" x14ac:dyDescent="0.4">
+      <c r="A11" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="24" t="s">
+      <c r="B11" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="C11" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="25">
+      <c r="D11" s="25">
         <v>2020</v>
       </c>
-      <c r="E10" s="25">
+      <c r="E11" s="25">
         <v>2021</v>
       </c>
-      <c r="F10" s="25">
+      <c r="F11" s="25">
         <v>2022</v>
       </c>
-      <c r="G10" s="25">
+      <c r="G11" s="25">
         <v>2023</v>
       </c>
-      <c r="H10" s="25">
+      <c r="H11" s="25">
         <v>2024</v>
       </c>
-      <c r="I10" s="25">
+      <c r="I11" s="25">
         <v>2025</v>
       </c>
-      <c r="J10" s="25">
+      <c r="J11" s="25">
         <v>2026</v>
       </c>
-      <c r="K10" s="25">
+      <c r="K11" s="25">
         <v>2027</v>
       </c>
-      <c r="L10" s="25">
+      <c r="L11" s="25">
         <v>2028</v>
       </c>
-      <c r="M10" s="25">
+      <c r="M11" s="25">
         <v>2029</v>
       </c>
-      <c r="N10" s="25">
+      <c r="N11" s="25">
         <v>2030</v>
       </c>
-      <c r="O10" s="25">
+      <c r="O11" s="25">
         <v>2031</v>
       </c>
-      <c r="P10" s="25">
+      <c r="P11" s="25">
         <v>2032</v>
       </c>
-      <c r="Q10" s="25">
+      <c r="Q11" s="25">
         <v>2033</v>
       </c>
-      <c r="R10" s="25">
+      <c r="R11" s="25">
         <v>2034</v>
       </c>
-      <c r="S10" s="25">
+      <c r="S11" s="25">
         <v>2035</v>
       </c>
-      <c r="T10" s="25">
+      <c r="T11" s="25">
         <v>2036</v>
       </c>
-      <c r="U10" s="25">
+      <c r="U11" s="25">
         <v>2037</v>
       </c>
-      <c r="V10" s="25">
+      <c r="V11" s="25">
         <v>2038</v>
       </c>
-      <c r="W10" s="25">
+      <c r="W11" s="25">
         <v>2039</v>
       </c>
-      <c r="X10" s="25">
+      <c r="X11" s="25">
         <v>2040</v>
       </c>
-      <c r="Y10" s="25">
+      <c r="Y11" s="25">
         <v>2041</v>
       </c>
-      <c r="Z10" s="25">
+      <c r="Z11" s="25">
         <v>2042</v>
       </c>
-      <c r="AA10" s="25">
+      <c r="AA11" s="25">
         <v>2043</v>
       </c>
-      <c r="AB10" s="25">
+      <c r="AB11" s="25">
         <v>2044</v>
       </c>
-      <c r="AC10" s="25">
+      <c r="AC11" s="25">
         <v>2045</v>
       </c>
-      <c r="AD10" s="25">
+      <c r="AD11" s="25">
         <v>2046</v>
       </c>
-      <c r="AE10" s="25">
+      <c r="AE11" s="25">
         <v>2047</v>
       </c>
-      <c r="AF10" s="25">
+      <c r="AF11" s="25">
         <v>2048</v>
       </c>
-      <c r="AG10" s="25">
+      <c r="AG11" s="25">
         <v>2049</v>
       </c>
-      <c r="AH10" s="25">
+      <c r="AH11" s="25">
         <v>2050</v>
       </c>
-      <c r="AI10" s="25">
+      <c r="AI11" s="25">
         <v>2051</v>
       </c>
-      <c r="AJ10" s="25">
+      <c r="AJ11" s="25">
         <v>2052</v>
       </c>
-      <c r="AK10" s="25">
+      <c r="AK11" s="25">
         <v>2053</v>
       </c>
-      <c r="AL10" s="25">
+      <c r="AL11" s="25">
         <v>2054</v>
       </c>
-      <c r="AM10" s="25">
+      <c r="AM11" s="25">
         <v>2055</v>
       </c>
-      <c r="AN10" s="25">
+      <c r="AN11" s="25">
         <v>2056</v>
       </c>
-      <c r="AO10" s="25">
+      <c r="AO11" s="25">
         <v>2057</v>
       </c>
-      <c r="AP10" s="25">
+      <c r="AP11" s="25">
         <v>2058</v>
       </c>
-      <c r="AQ10" s="25">
+      <c r="AQ11" s="25">
         <v>2059</v>
       </c>
-      <c r="AR10" s="25">
+      <c r="AR11" s="25">
         <v>2060</v>
-      </c>
-      <c r="AS10" s="15"/>
-      <c r="AT10" s="15"/>
-    </row>
-    <row r="11" spans="1:46" ht="16" x14ac:dyDescent="0.4">
-      <c r="A11" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="C11" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="H11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="I11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="J11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="K11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="L11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="M11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="N11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="O11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="P11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="R11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="S11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="T11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="U11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="V11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="W11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="X11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="Z11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AA11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AB11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AC11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AD11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AE11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AF11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AG11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AH11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AI11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AJ11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AK11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AL11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AM11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AN11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AO11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AP11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AQ11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AR11" s="19" t="s">
-        <v>15</v>
       </c>
       <c r="AS11" s="15"/>
       <c r="AT11" s="15"/>
     </row>
     <row r="12" spans="1:46" ht="16" x14ac:dyDescent="0.4">
       <c r="A12" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D12" s="17">
-        <v>0</v>
-      </c>
-      <c r="E12" s="17">
-        <v>0</v>
-      </c>
-      <c r="F12" s="17">
-        <v>0</v>
-      </c>
-      <c r="G12" s="17">
-        <v>0</v>
-      </c>
-      <c r="H12" s="17">
-        <v>0</v>
-      </c>
-      <c r="I12" s="17">
-        <v>0</v>
-      </c>
-      <c r="J12" s="17">
-        <v>0</v>
-      </c>
-      <c r="K12" s="17">
-        <v>0</v>
-      </c>
-      <c r="L12" s="17">
-        <v>0</v>
-      </c>
-      <c r="M12" s="17">
-        <v>0</v>
-      </c>
-      <c r="N12" s="17">
-        <v>0</v>
-      </c>
-      <c r="O12" s="17">
-        <v>0</v>
-      </c>
-      <c r="P12" s="17">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="17">
-        <v>0</v>
-      </c>
-      <c r="R12" s="17">
-        <v>0</v>
-      </c>
-      <c r="S12" s="17">
-        <v>0</v>
-      </c>
-      <c r="T12" s="17">
-        <v>0</v>
-      </c>
-      <c r="U12" s="17">
-        <v>0</v>
-      </c>
-      <c r="V12" s="17">
-        <v>0</v>
-      </c>
-      <c r="W12" s="17">
-        <v>0</v>
-      </c>
-      <c r="X12" s="17">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="17">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AA12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AB12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AC12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AD12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AE12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AF12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AG12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AH12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AI12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AJ12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AK12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AL12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AM12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AN12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AO12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AP12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AQ12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AR12" s="17">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="J12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="K12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="L12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="M12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="N12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="O12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="P12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="R12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="S12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="T12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="U12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="V12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="W12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="X12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AF12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AI12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AJ12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AL12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AN12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AO12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AP12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AR12" s="19" t="s">
+        <v>15</v>
       </c>
       <c r="AS12" s="15"/>
       <c r="AT12" s="15"/>
     </row>
     <row r="13" spans="1:46" ht="16" x14ac:dyDescent="0.4">
-      <c r="A13" s="23"/>
-      <c r="B13" s="23"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="21"/>
-      <c r="K13" s="21"/>
-      <c r="L13" s="21"/>
-      <c r="M13" s="21"/>
-      <c r="N13" s="21"/>
-      <c r="O13" s="21"/>
-      <c r="P13" s="21"/>
-      <c r="Q13" s="21"/>
-      <c r="R13" s="21"/>
-      <c r="S13" s="21"/>
-      <c r="T13" s="21"/>
-      <c r="U13" s="21"/>
-      <c r="V13" s="21"/>
-      <c r="W13" s="21"/>
-      <c r="X13" s="21"/>
-      <c r="Y13" s="21"/>
-      <c r="Z13" s="21"/>
-      <c r="AA13" s="21"/>
-      <c r="AB13" s="21"/>
-      <c r="AC13" s="21"/>
-      <c r="AD13" s="21"/>
-      <c r="AE13" s="21"/>
-      <c r="AF13" s="21"/>
-      <c r="AG13" s="21"/>
-      <c r="AH13" s="21"/>
-      <c r="AI13" s="21"/>
-      <c r="AJ13" s="21"/>
-      <c r="AK13" s="21"/>
-      <c r="AL13" s="21"/>
-      <c r="AM13" s="21"/>
-      <c r="AN13" s="21"/>
-      <c r="AO13" s="21"/>
-      <c r="AP13" s="21"/>
-      <c r="AQ13" s="21"/>
-      <c r="AR13" s="21"/>
+      <c r="A13" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="17">
+        <v>0</v>
+      </c>
+      <c r="E13" s="17">
+        <v>0</v>
+      </c>
+      <c r="F13" s="17">
+        <v>0</v>
+      </c>
+      <c r="G13" s="17">
+        <v>0</v>
+      </c>
+      <c r="H13" s="17">
+        <v>0</v>
+      </c>
+      <c r="I13" s="17">
+        <v>0</v>
+      </c>
+      <c r="J13" s="17">
+        <v>0</v>
+      </c>
+      <c r="K13" s="17">
+        <v>0</v>
+      </c>
+      <c r="L13" s="17">
+        <v>0</v>
+      </c>
+      <c r="M13" s="17">
+        <v>0</v>
+      </c>
+      <c r="N13" s="17">
+        <v>0</v>
+      </c>
+      <c r="O13" s="17">
+        <v>0</v>
+      </c>
+      <c r="P13" s="17">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="17">
+        <v>0</v>
+      </c>
+      <c r="R13" s="17">
+        <v>0</v>
+      </c>
+      <c r="S13" s="17">
+        <v>0</v>
+      </c>
+      <c r="T13" s="17">
+        <v>0</v>
+      </c>
+      <c r="U13" s="17">
+        <v>0</v>
+      </c>
+      <c r="V13" s="17">
+        <v>0</v>
+      </c>
+      <c r="W13" s="17">
+        <v>0</v>
+      </c>
+      <c r="X13" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AM13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AN13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AP13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AR13" s="17">
+        <v>0</v>
+      </c>
       <c r="AS13" s="15"/>
       <c r="AT13" s="15"/>
     </row>
     <row r="14" spans="1:46" ht="16" x14ac:dyDescent="0.4">
-      <c r="A14" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="11">
-        <v>2020</v>
-      </c>
-      <c r="E14" s="11">
-        <v>2021</v>
-      </c>
-      <c r="F14" s="11">
-        <v>2022</v>
-      </c>
-      <c r="G14" s="11">
-        <v>2023</v>
-      </c>
-      <c r="H14" s="11">
-        <v>2024</v>
-      </c>
-      <c r="I14" s="11">
-        <v>2025</v>
-      </c>
-      <c r="J14" s="11">
-        <v>2026</v>
-      </c>
-      <c r="K14" s="11">
-        <v>2027</v>
-      </c>
-      <c r="L14" s="11">
-        <v>2028</v>
-      </c>
-      <c r="M14" s="11">
-        <v>2029</v>
-      </c>
-      <c r="N14" s="11">
-        <v>2030</v>
-      </c>
-      <c r="O14" s="11">
-        <v>2031</v>
-      </c>
-      <c r="P14" s="11">
-        <v>2032</v>
-      </c>
-      <c r="Q14" s="11">
-        <v>2033</v>
-      </c>
-      <c r="R14" s="11">
-        <v>2034</v>
-      </c>
-      <c r="S14" s="11">
-        <v>2035</v>
-      </c>
-      <c r="T14" s="11">
-        <v>2036</v>
-      </c>
-      <c r="U14" s="11">
-        <v>2037</v>
-      </c>
-      <c r="V14" s="11">
-        <v>2038</v>
-      </c>
-      <c r="W14" s="11">
-        <v>2039</v>
-      </c>
-      <c r="X14" s="11">
-        <v>2040</v>
-      </c>
-      <c r="Y14" s="11">
-        <v>2041</v>
-      </c>
-      <c r="Z14" s="11">
-        <v>2042</v>
-      </c>
-      <c r="AA14" s="11">
-        <v>2043</v>
-      </c>
-      <c r="AB14" s="11">
-        <v>2044</v>
-      </c>
-      <c r="AC14" s="11">
-        <v>2045</v>
-      </c>
-      <c r="AD14" s="11">
-        <v>2046</v>
-      </c>
-      <c r="AE14" s="11">
-        <v>2047</v>
-      </c>
-      <c r="AF14" s="11">
-        <v>2048</v>
-      </c>
-      <c r="AG14" s="11">
-        <v>2049</v>
-      </c>
-      <c r="AH14" s="11">
-        <v>2050</v>
-      </c>
-      <c r="AI14" s="11">
-        <v>2051</v>
-      </c>
-      <c r="AJ14" s="11">
-        <v>2052</v>
-      </c>
-      <c r="AK14" s="11">
-        <v>2053</v>
-      </c>
-      <c r="AL14" s="11">
-        <v>2054</v>
-      </c>
-      <c r="AM14" s="11">
-        <v>2055</v>
-      </c>
-      <c r="AN14" s="11">
-        <v>2056</v>
-      </c>
-      <c r="AO14" s="11">
-        <v>2057</v>
-      </c>
-      <c r="AP14" s="11">
-        <v>2058</v>
-      </c>
-      <c r="AQ14" s="11">
-        <v>2059</v>
-      </c>
-      <c r="AR14" s="11">
-        <v>2060</v>
-      </c>
+      <c r="A14" s="23"/>
+      <c r="B14" s="23"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="21"/>
+      <c r="L14" s="21"/>
+      <c r="M14" s="21"/>
+      <c r="N14" s="21"/>
+      <c r="O14" s="21"/>
+      <c r="P14" s="21"/>
+      <c r="Q14" s="21"/>
+      <c r="R14" s="21"/>
+      <c r="S14" s="21"/>
+      <c r="T14" s="21"/>
+      <c r="U14" s="21"/>
+      <c r="V14" s="21"/>
+      <c r="W14" s="21"/>
+      <c r="X14" s="21"/>
+      <c r="Y14" s="21"/>
+      <c r="Z14" s="21"/>
+      <c r="AA14" s="21"/>
+      <c r="AB14" s="21"/>
+      <c r="AC14" s="21"/>
+      <c r="AD14" s="21"/>
+      <c r="AE14" s="21"/>
+      <c r="AF14" s="21"/>
+      <c r="AG14" s="21"/>
+      <c r="AH14" s="21"/>
+      <c r="AI14" s="21"/>
+      <c r="AJ14" s="21"/>
+      <c r="AK14" s="21"/>
+      <c r="AL14" s="21"/>
+      <c r="AM14" s="21"/>
+      <c r="AN14" s="21"/>
+      <c r="AO14" s="21"/>
+      <c r="AP14" s="21"/>
+      <c r="AQ14" s="21"/>
+      <c r="AR14" s="21"/>
       <c r="AS14" s="15"/>
       <c r="AT14" s="15"/>
     </row>
     <row r="15" spans="1:46" ht="16" x14ac:dyDescent="0.4">
-      <c r="A15" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" s="17">
-        <v>0</v>
-      </c>
-      <c r="E15" s="17">
-        <v>0</v>
-      </c>
-      <c r="F15" s="17">
-        <v>0</v>
-      </c>
-      <c r="G15" s="17">
-        <v>0</v>
-      </c>
-      <c r="H15" s="17">
-        <v>0</v>
-      </c>
-      <c r="I15" s="17">
-        <v>0</v>
-      </c>
-      <c r="J15" s="17">
-        <v>0</v>
-      </c>
-      <c r="K15" s="17">
-        <v>0</v>
-      </c>
-      <c r="L15" s="17">
-        <v>0</v>
-      </c>
-      <c r="M15" s="17">
-        <v>0</v>
-      </c>
-      <c r="N15" s="17">
-        <v>0</v>
-      </c>
-      <c r="O15" s="17">
-        <v>0</v>
-      </c>
-      <c r="P15" s="17">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="17">
-        <v>0</v>
-      </c>
-      <c r="R15" s="17">
-        <v>0</v>
-      </c>
-      <c r="S15" s="17">
-        <v>0</v>
-      </c>
-      <c r="T15" s="17">
-        <v>0</v>
-      </c>
-      <c r="U15" s="17">
-        <v>0</v>
-      </c>
-      <c r="V15" s="17">
-        <v>0</v>
-      </c>
-      <c r="W15" s="17">
-        <v>0</v>
-      </c>
-      <c r="X15" s="17">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="17">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AC15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AD15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AE15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AF15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AG15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AH15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AI15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AJ15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AK15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AL15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AM15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AN15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AO15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AP15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AQ15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AR15" s="17">
-        <v>0</v>
+      <c r="A15" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="11">
+        <v>2020</v>
+      </c>
+      <c r="E15" s="11">
+        <v>2021</v>
+      </c>
+      <c r="F15" s="11">
+        <v>2022</v>
+      </c>
+      <c r="G15" s="11">
+        <v>2023</v>
+      </c>
+      <c r="H15" s="11">
+        <v>2024</v>
+      </c>
+      <c r="I15" s="11">
+        <v>2025</v>
+      </c>
+      <c r="J15" s="11">
+        <v>2026</v>
+      </c>
+      <c r="K15" s="11">
+        <v>2027</v>
+      </c>
+      <c r="L15" s="11">
+        <v>2028</v>
+      </c>
+      <c r="M15" s="11">
+        <v>2029</v>
+      </c>
+      <c r="N15" s="11">
+        <v>2030</v>
+      </c>
+      <c r="O15" s="11">
+        <v>2031</v>
+      </c>
+      <c r="P15" s="11">
+        <v>2032</v>
+      </c>
+      <c r="Q15" s="11">
+        <v>2033</v>
+      </c>
+      <c r="R15" s="11">
+        <v>2034</v>
+      </c>
+      <c r="S15" s="11">
+        <v>2035</v>
+      </c>
+      <c r="T15" s="11">
+        <v>2036</v>
+      </c>
+      <c r="U15" s="11">
+        <v>2037</v>
+      </c>
+      <c r="V15" s="11">
+        <v>2038</v>
+      </c>
+      <c r="W15" s="11">
+        <v>2039</v>
+      </c>
+      <c r="X15" s="11">
+        <v>2040</v>
+      </c>
+      <c r="Y15" s="11">
+        <v>2041</v>
+      </c>
+      <c r="Z15" s="11">
+        <v>2042</v>
+      </c>
+      <c r="AA15" s="11">
+        <v>2043</v>
+      </c>
+      <c r="AB15" s="11">
+        <v>2044</v>
+      </c>
+      <c r="AC15" s="11">
+        <v>2045</v>
+      </c>
+      <c r="AD15" s="11">
+        <v>2046</v>
+      </c>
+      <c r="AE15" s="11">
+        <v>2047</v>
+      </c>
+      <c r="AF15" s="11">
+        <v>2048</v>
+      </c>
+      <c r="AG15" s="11">
+        <v>2049</v>
+      </c>
+      <c r="AH15" s="11">
+        <v>2050</v>
+      </c>
+      <c r="AI15" s="11">
+        <v>2051</v>
+      </c>
+      <c r="AJ15" s="11">
+        <v>2052</v>
+      </c>
+      <c r="AK15" s="11">
+        <v>2053</v>
+      </c>
+      <c r="AL15" s="11">
+        <v>2054</v>
+      </c>
+      <c r="AM15" s="11">
+        <v>2055</v>
+      </c>
+      <c r="AN15" s="11">
+        <v>2056</v>
+      </c>
+      <c r="AO15" s="11">
+        <v>2057</v>
+      </c>
+      <c r="AP15" s="11">
+        <v>2058</v>
+      </c>
+      <c r="AQ15" s="11">
+        <v>2059</v>
+      </c>
+      <c r="AR15" s="11">
+        <v>2060</v>
       </c>
       <c r="AS15" s="15"/>
       <c r="AT15" s="15"/>
     </row>
     <row r="16" spans="1:46" ht="16" x14ac:dyDescent="0.4">
-      <c r="A16" s="15"/>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="15"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="15"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="15"/>
-      <c r="N16" s="15"/>
-      <c r="O16" s="15"/>
-      <c r="P16" s="15"/>
-      <c r="Q16" s="15"/>
-      <c r="R16" s="15"/>
-      <c r="S16" s="15"/>
-      <c r="T16" s="15"/>
-      <c r="U16" s="15"/>
-      <c r="V16" s="15"/>
-      <c r="W16" s="15"/>
-      <c r="X16" s="15"/>
-      <c r="Y16" s="15"/>
-      <c r="Z16" s="15"/>
-      <c r="AA16" s="15"/>
-      <c r="AB16" s="15"/>
-      <c r="AC16" s="15"/>
-      <c r="AD16" s="15"/>
-      <c r="AE16" s="15"/>
-      <c r="AF16" s="15"/>
-      <c r="AG16" s="15"/>
-      <c r="AH16" s="15"/>
-      <c r="AI16" s="15"/>
-      <c r="AJ16" s="16"/>
-      <c r="AK16" s="16"/>
-      <c r="AL16" s="15"/>
-      <c r="AM16" s="16"/>
-      <c r="AN16" s="16"/>
-      <c r="AO16" s="15"/>
-      <c r="AP16" s="15"/>
-      <c r="AQ16" s="15"/>
-      <c r="AR16" s="15"/>
-    </row>
-    <row r="17" spans="1:44" s="3" customFormat="1" ht="16" x14ac:dyDescent="0.35">
-      <c r="A17" s="10" t="s">
+      <c r="A16" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" s="17">
+        <v>0</v>
+      </c>
+      <c r="E16" s="17">
+        <v>0</v>
+      </c>
+      <c r="F16" s="17">
+        <v>0</v>
+      </c>
+      <c r="G16" s="17">
+        <v>0</v>
+      </c>
+      <c r="H16" s="17">
+        <v>0</v>
+      </c>
+      <c r="I16" s="17">
+        <v>0</v>
+      </c>
+      <c r="J16" s="17">
+        <v>0</v>
+      </c>
+      <c r="K16" s="17">
+        <v>0</v>
+      </c>
+      <c r="L16" s="17">
+        <v>0</v>
+      </c>
+      <c r="M16" s="17">
+        <v>0</v>
+      </c>
+      <c r="N16" s="17">
+        <v>0</v>
+      </c>
+      <c r="O16" s="17">
+        <v>0</v>
+      </c>
+      <c r="P16" s="17">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="17">
+        <v>0</v>
+      </c>
+      <c r="R16" s="17">
+        <v>0</v>
+      </c>
+      <c r="S16" s="17">
+        <v>0</v>
+      </c>
+      <c r="T16" s="17">
+        <v>0</v>
+      </c>
+      <c r="U16" s="17">
+        <v>0</v>
+      </c>
+      <c r="V16" s="17">
+        <v>0</v>
+      </c>
+      <c r="W16" s="17">
+        <v>0</v>
+      </c>
+      <c r="X16" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AF16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AG16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AH16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AI16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AJ16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AK16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AL16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AM16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AN16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AO16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AP16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AQ16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AR16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AS16" s="15"/>
+      <c r="AT16" s="15"/>
+    </row>
+    <row r="17" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A17" s="15"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="15"/>
+      <c r="M17" s="15"/>
+      <c r="N17" s="15"/>
+      <c r="O17" s="15"/>
+      <c r="P17" s="15"/>
+      <c r="Q17" s="15"/>
+      <c r="R17" s="15"/>
+      <c r="S17" s="15"/>
+      <c r="T17" s="15"/>
+      <c r="U17" s="15"/>
+      <c r="V17" s="15"/>
+      <c r="W17" s="15"/>
+      <c r="X17" s="15"/>
+      <c r="Y17" s="15"/>
+      <c r="Z17" s="15"/>
+      <c r="AA17" s="15"/>
+      <c r="AB17" s="15"/>
+      <c r="AC17" s="15"/>
+      <c r="AD17" s="15"/>
+      <c r="AE17" s="15"/>
+      <c r="AF17" s="15"/>
+      <c r="AG17" s="15"/>
+      <c r="AH17" s="15"/>
+      <c r="AI17" s="15"/>
+      <c r="AJ17" s="16"/>
+      <c r="AK17" s="16"/>
+      <c r="AL17" s="15"/>
+      <c r="AM17" s="16"/>
+      <c r="AN17" s="16"/>
+      <c r="AO17" s="15"/>
+      <c r="AP17" s="15"/>
+      <c r="AQ17" s="15"/>
+      <c r="AR17" s="15"/>
+    </row>
+    <row r="18" spans="1:44" s="3" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A18" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B18" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C18" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="12"/>
-      <c r="J17" s="12"/>
-      <c r="K17" s="12"/>
-      <c r="L17" s="12"/>
-      <c r="M17" s="12"/>
-      <c r="N17" s="12"/>
-      <c r="O17" s="12"/>
-      <c r="P17" s="12"/>
-      <c r="Q17" s="12"/>
-      <c r="R17" s="12"/>
-      <c r="S17" s="12"/>
-      <c r="T17" s="12"/>
-      <c r="U17" s="12"/>
-      <c r="V17" s="12"/>
-      <c r="W17" s="12"/>
-      <c r="X17" s="12"/>
-      <c r="Y17" s="12"/>
-      <c r="Z17" s="12"/>
-      <c r="AA17" s="12"/>
-      <c r="AB17" s="12"/>
-      <c r="AC17" s="12"/>
-      <c r="AD17" s="12"/>
-      <c r="AE17" s="12"/>
-      <c r="AF17" s="12"/>
-      <c r="AG17" s="12"/>
-      <c r="AH17" s="12"/>
-      <c r="AI17" s="12"/>
-      <c r="AJ17" s="12"/>
-      <c r="AK17" s="12"/>
-      <c r="AL17" s="12"/>
-      <c r="AM17" s="12"/>
-      <c r="AN17" s="12"/>
-      <c r="AO17" s="12"/>
-      <c r="AP17" s="12"/>
-      <c r="AQ17" s="12"/>
-      <c r="AR17" s="12"/>
-    </row>
-    <row r="18" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A18" s="13" t="s">
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="12"/>
+      <c r="M18" s="12"/>
+      <c r="N18" s="12"/>
+      <c r="O18" s="12"/>
+      <c r="P18" s="12"/>
+      <c r="Q18" s="12"/>
+      <c r="R18" s="12"/>
+      <c r="S18" s="12"/>
+      <c r="T18" s="12"/>
+      <c r="U18" s="12"/>
+      <c r="V18" s="12"/>
+      <c r="W18" s="12"/>
+      <c r="X18" s="12"/>
+      <c r="Y18" s="12"/>
+      <c r="Z18" s="12"/>
+      <c r="AA18" s="12"/>
+      <c r="AB18" s="12"/>
+      <c r="AC18" s="12"/>
+      <c r="AD18" s="12"/>
+      <c r="AE18" s="12"/>
+      <c r="AF18" s="12"/>
+      <c r="AG18" s="12"/>
+      <c r="AH18" s="12"/>
+      <c r="AI18" s="12"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="12"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+    </row>
+    <row r="19" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A19" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="14">
-        <v>0</v>
-      </c>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8"/>
-      <c r="L18" s="8"/>
-      <c r="M18" s="8"/>
-      <c r="N18" s="8"/>
-      <c r="O18" s="8"/>
-      <c r="P18" s="8"/>
-      <c r="Q18" s="8"/>
-      <c r="R18" s="8"/>
-      <c r="S18" s="8"/>
-      <c r="T18" s="8"/>
-      <c r="U18" s="8"/>
-      <c r="V18" s="15"/>
-      <c r="W18" s="15"/>
-      <c r="X18" s="15"/>
-      <c r="Y18" s="15"/>
-      <c r="Z18" s="15"/>
-      <c r="AA18" s="15"/>
-      <c r="AB18" s="15"/>
-      <c r="AC18" s="15"/>
-      <c r="AD18" s="15"/>
-      <c r="AE18" s="15"/>
-      <c r="AF18" s="15"/>
-      <c r="AG18" s="15"/>
-      <c r="AH18" s="15"/>
-      <c r="AI18" s="15"/>
-      <c r="AJ18" s="15"/>
-      <c r="AK18" s="15"/>
-      <c r="AL18" s="15"/>
-      <c r="AM18" s="16"/>
-      <c r="AN18" s="16"/>
-      <c r="AO18" s="15"/>
-      <c r="AP18" s="15"/>
-      <c r="AQ18" s="15"/>
-      <c r="AR18" s="15"/>
-    </row>
-    <row r="19" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="1"/>
+      <c r="C19" s="14">
+        <v>0</v>
+      </c>
       <c r="D19" s="8"/>
       <c r="E19" s="8"/>
       <c r="F19" s="8"/>
@@ -2473,15 +2289,9 @@
       <c r="AR19" s="15"/>
     </row>
     <row r="20" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A20" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>8</v>
-      </c>
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="1"/>
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="8"/>
@@ -2525,14 +2335,14 @@
       <c r="AR20" s="15"/>
     </row>
     <row r="21" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A21" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="17">
-        <v>0</v>
+      <c r="A21" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>8</v>
       </c>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
@@ -2544,7 +2354,7 @@
       <c r="K21" s="8"/>
       <c r="L21" s="8"/>
       <c r="M21" s="8"/>
-      <c r="N21" s="2"/>
+      <c r="N21" s="8"/>
       <c r="O21" s="8"/>
       <c r="P21" s="8"/>
       <c r="Q21" s="8"/>
@@ -2578,7 +2388,7 @@
     </row>
     <row r="22" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A22" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>6</v>
@@ -2630,7 +2440,7 @@
     </row>
     <row r="23" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A23" s="5" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>6</v>
@@ -2648,7 +2458,7 @@
       <c r="K23" s="8"/>
       <c r="L23" s="8"/>
       <c r="M23" s="8"/>
-      <c r="N23" s="8"/>
+      <c r="N23" s="2"/>
       <c r="O23" s="8"/>
       <c r="P23" s="8"/>
       <c r="Q23" s="8"/>
@@ -2680,62 +2490,68 @@
       <c r="AQ23" s="15"/>
       <c r="AR23" s="15"/>
     </row>
-    <row r="24" spans="1:44" ht="16" x14ac:dyDescent="0.35">
-      <c r="A24" s="20" t="s">
+    <row r="24" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A24" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="17">
+        <v>0</v>
+      </c>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="N24" s="8"/>
+      <c r="O24" s="8"/>
+      <c r="P24" s="8"/>
+      <c r="Q24" s="8"/>
+      <c r="R24" s="8"/>
+      <c r="S24" s="8"/>
+      <c r="T24" s="8"/>
+      <c r="U24" s="8"/>
+      <c r="V24" s="15"/>
+      <c r="W24" s="15"/>
+      <c r="X24" s="15"/>
+      <c r="Y24" s="15"/>
+      <c r="Z24" s="15"/>
+      <c r="AA24" s="15"/>
+      <c r="AB24" s="15"/>
+      <c r="AC24" s="15"/>
+      <c r="AD24" s="15"/>
+      <c r="AE24" s="15"/>
+      <c r="AF24" s="15"/>
+      <c r="AG24" s="15"/>
+      <c r="AH24" s="15"/>
+      <c r="AI24" s="15"/>
+      <c r="AJ24" s="15"/>
+      <c r="AK24" s="15"/>
+      <c r="AL24" s="15"/>
+      <c r="AM24" s="16"/>
+      <c r="AN24" s="16"/>
+      <c r="AO24" s="15"/>
+      <c r="AP24" s="15"/>
+      <c r="AQ24" s="15"/>
+      <c r="AR24" s="15"/>
+    </row>
+    <row r="25" spans="1:44" ht="16" x14ac:dyDescent="0.35">
+      <c r="A25" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C24" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A25" s="15"/>
-      <c r="B25" s="15"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="15"/>
-      <c r="I25" s="15"/>
-      <c r="J25" s="15"/>
-      <c r="K25" s="15"/>
-      <c r="L25" s="15"/>
-      <c r="M25" s="15"/>
-      <c r="N25" s="15"/>
-      <c r="O25" s="15"/>
-      <c r="P25" s="15"/>
-      <c r="Q25" s="15"/>
-      <c r="R25" s="15"/>
-      <c r="S25" s="15"/>
-      <c r="T25" s="15"/>
-      <c r="U25" s="15"/>
-      <c r="V25" s="15"/>
-      <c r="W25" s="15"/>
-      <c r="X25" s="15"/>
-      <c r="Y25" s="15"/>
-      <c r="Z25" s="15"/>
-      <c r="AA25" s="15"/>
-      <c r="AB25" s="15"/>
-      <c r="AC25" s="15"/>
-      <c r="AD25" s="15"/>
-      <c r="AE25" s="15"/>
-      <c r="AF25" s="15"/>
-      <c r="AG25" s="15"/>
-      <c r="AH25" s="15"/>
-      <c r="AI25" s="15"/>
-      <c r="AJ25" s="16"/>
-      <c r="AK25" s="16"/>
-      <c r="AL25" s="15"/>
-      <c r="AM25" s="16"/>
-      <c r="AN25" s="16"/>
-      <c r="AO25" s="15"/>
-      <c r="AP25" s="15"/>
-      <c r="AQ25" s="15"/>
-      <c r="AR25" s="15"/>
+      <c r="B25" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C25" s="14">
+        <v>0</v>
+      </c>
     </row>
     <row r="26" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A26" s="15"/>
@@ -2776,123 +2592,81 @@
       <c r="AJ26" s="16"/>
       <c r="AK26" s="16"/>
       <c r="AL26" s="15"/>
-      <c r="AM26" s="15"/>
-      <c r="AN26" s="15"/>
+      <c r="AM26" s="16"/>
+      <c r="AN26" s="16"/>
       <c r="AO26" s="15"/>
       <c r="AP26" s="15"/>
       <c r="AQ26" s="15"/>
       <c r="AR26" s="15"/>
     </row>
-    <row r="33" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="34" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="35" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="36" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="37" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="38" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="39" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="40" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="41" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="42" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="43" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="44" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="45" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="46" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="47" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="48" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="49" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="50" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="51" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="52" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="53" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="54" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="55" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="56" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="57" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="58" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="59" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="60" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="61" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="62" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="63" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="64" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="66" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="67" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="68" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="69" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="70" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="71" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="72" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="73" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="74" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="75" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="76" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="77" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="78" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="79" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="80" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="81" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="82" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="83" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="84" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="85" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="86" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="87" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="88" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="89" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="90" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="91" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="92" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="93" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="94" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="95" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="96" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="97" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="98" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="99" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="100" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="101" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="102" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="103" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="104" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="105" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="106" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="107" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="108" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="109" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="110" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="111" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="112" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="113" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="114" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="115" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="116" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="117" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="118" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="119" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="120" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="27" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A27" s="15"/>
+      <c r="B27" s="15"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="15"/>
+      <c r="J27" s="15"/>
+      <c r="K27" s="15"/>
+      <c r="L27" s="15"/>
+      <c r="M27" s="15"/>
+      <c r="N27" s="15"/>
+      <c r="O27" s="15"/>
+      <c r="P27" s="15"/>
+      <c r="Q27" s="15"/>
+      <c r="R27" s="15"/>
+      <c r="S27" s="15"/>
+      <c r="T27" s="15"/>
+      <c r="U27" s="15"/>
+      <c r="V27" s="15"/>
+      <c r="W27" s="15"/>
+      <c r="X27" s="15"/>
+      <c r="Y27" s="15"/>
+      <c r="Z27" s="15"/>
+      <c r="AA27" s="15"/>
+      <c r="AB27" s="15"/>
+      <c r="AC27" s="15"/>
+      <c r="AD27" s="15"/>
+      <c r="AE27" s="15"/>
+      <c r="AF27" s="15"/>
+      <c r="AG27" s="15"/>
+      <c r="AH27" s="15"/>
+      <c r="AI27" s="15"/>
+      <c r="AJ27" s="16"/>
+      <c r="AK27" s="16"/>
+      <c r="AL27" s="15"/>
+      <c r="AM27" s="15"/>
+      <c r="AN27" s="15"/>
+      <c r="AO27" s="15"/>
+      <c r="AP27" s="15"/>
+      <c r="AQ27" s="15"/>
+      <c r="AR27" s="15"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A11:A13">
-    <cfRule type="cellIs" dxfId="37" priority="1" operator="equal">
+  <conditionalFormatting sqref="A12:A14">
+    <cfRule type="cellIs" dxfId="17" priority="1" operator="equal">
       <formula>"increase debt"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="36" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="16" priority="2" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B11">
-    <cfRule type="cellIs" dxfId="35" priority="3" operator="equal">
+  <conditionalFormatting sqref="B12">
+    <cfRule type="cellIs" dxfId="15" priority="3" operator="equal">
       <formula>"increase debt"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="34" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="14" priority="4" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B5:AJ5">
-    <cfRule type="cellIs" dxfId="31" priority="7" operator="equal">
+  <conditionalFormatting sqref="B6:AJ6">
+    <cfRule type="cellIs" dxfId="13" priority="7" operator="equal">
       <formula>"increase debt"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="30" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="12" priority="8" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2903,7 +2677,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5C54003D-BBE9-46A5-976B-0C15632AF571}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:AT26"/>
+  <dimension ref="A1:AT27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="30.6328125" customWidth="1"/>
@@ -3119,15 +2893,13 @@
       <c r="AR4" s="15"/>
     </row>
     <row r="5" spans="1:46" ht="16" x14ac:dyDescent="0.4">
-      <c r="A5" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>15</v>
-      </c>
+      <c r="A5" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="14"/>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
@@ -3171,14 +2943,14 @@
       <c r="AR5" s="15"/>
     </row>
     <row r="6" spans="1:46" ht="16" x14ac:dyDescent="0.4">
-      <c r="A6" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C6" s="17">
-        <v>0</v>
+      <c r="A6" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>15</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
@@ -3215,8 +2987,8 @@
       <c r="AJ6" s="16"/>
       <c r="AK6" s="16"/>
       <c r="AL6" s="15"/>
-      <c r="AM6" s="16"/>
-      <c r="AN6" s="16"/>
+      <c r="AM6" s="15"/>
+      <c r="AN6" s="15"/>
       <c r="AO6" s="15"/>
       <c r="AP6" s="15"/>
       <c r="AQ6" s="15"/>
@@ -3224,10 +2996,10 @@
     </row>
     <row r="7" spans="1:46" ht="16" x14ac:dyDescent="0.4">
       <c r="A7" s="13" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C7" s="17">
         <v>0</v>
@@ -3264,8 +3036,8 @@
       <c r="AG7" s="15"/>
       <c r="AH7" s="15"/>
       <c r="AI7" s="15"/>
-      <c r="AJ7" s="15"/>
-      <c r="AK7" s="15"/>
+      <c r="AJ7" s="16"/>
+      <c r="AK7" s="16"/>
       <c r="AL7" s="15"/>
       <c r="AM7" s="16"/>
       <c r="AN7" s="16"/>
@@ -3276,7 +3048,7 @@
     </row>
     <row r="8" spans="1:46" ht="16" x14ac:dyDescent="0.4">
       <c r="A8" s="13" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>2</v>
@@ -3327,9 +3099,15 @@
       <c r="AR8" s="15"/>
     </row>
     <row r="9" spans="1:46" ht="16" x14ac:dyDescent="0.4">
-      <c r="A9" s="8"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="21"/>
+      <c r="A9" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="17">
+        <v>0</v>
+      </c>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
       <c r="F9" s="8"/>
@@ -3373,887 +3151,887 @@
       <c r="AR9" s="15"/>
     </row>
     <row r="10" spans="1:46" ht="16" x14ac:dyDescent="0.4">
-      <c r="A10" s="24" t="s">
+      <c r="A10" s="8"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8"/>
+      <c r="Q10" s="8"/>
+      <c r="R10" s="8"/>
+      <c r="S10" s="15"/>
+      <c r="T10" s="15"/>
+      <c r="U10" s="15"/>
+      <c r="V10" s="15"/>
+      <c r="W10" s="15"/>
+      <c r="X10" s="15"/>
+      <c r="Y10" s="15"/>
+      <c r="Z10" s="15"/>
+      <c r="AA10" s="15"/>
+      <c r="AB10" s="15"/>
+      <c r="AC10" s="15"/>
+      <c r="AD10" s="15"/>
+      <c r="AE10" s="15"/>
+      <c r="AF10" s="15"/>
+      <c r="AG10" s="15"/>
+      <c r="AH10" s="15"/>
+      <c r="AI10" s="15"/>
+      <c r="AJ10" s="15"/>
+      <c r="AK10" s="15"/>
+      <c r="AL10" s="15"/>
+      <c r="AM10" s="16"/>
+      <c r="AN10" s="16"/>
+      <c r="AO10" s="15"/>
+      <c r="AP10" s="15"/>
+      <c r="AQ10" s="15"/>
+      <c r="AR10" s="15"/>
+    </row>
+    <row r="11" spans="1:46" ht="16" x14ac:dyDescent="0.4">
+      <c r="A11" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="24" t="s">
+      <c r="B11" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="C11" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="25">
+      <c r="D11" s="25">
         <v>2020</v>
       </c>
-      <c r="E10" s="25">
+      <c r="E11" s="25">
         <v>2021</v>
       </c>
-      <c r="F10" s="25">
+      <c r="F11" s="25">
         <v>2022</v>
       </c>
-      <c r="G10" s="25">
+      <c r="G11" s="25">
         <v>2023</v>
       </c>
-      <c r="H10" s="25">
+      <c r="H11" s="25">
         <v>2024</v>
       </c>
-      <c r="I10" s="25">
+      <c r="I11" s="25">
         <v>2025</v>
       </c>
-      <c r="J10" s="25">
+      <c r="J11" s="25">
         <v>2026</v>
       </c>
-      <c r="K10" s="25">
+      <c r="K11" s="25">
         <v>2027</v>
       </c>
-      <c r="L10" s="25">
+      <c r="L11" s="25">
         <v>2028</v>
       </c>
-      <c r="M10" s="25">
+      <c r="M11" s="25">
         <v>2029</v>
       </c>
-      <c r="N10" s="25">
+      <c r="N11" s="25">
         <v>2030</v>
       </c>
-      <c r="O10" s="25">
+      <c r="O11" s="25">
         <v>2031</v>
       </c>
-      <c r="P10" s="25">
+      <c r="P11" s="25">
         <v>2032</v>
       </c>
-      <c r="Q10" s="25">
+      <c r="Q11" s="25">
         <v>2033</v>
       </c>
-      <c r="R10" s="25">
+      <c r="R11" s="25">
         <v>2034</v>
       </c>
-      <c r="S10" s="25">
+      <c r="S11" s="25">
         <v>2035</v>
       </c>
-      <c r="T10" s="25">
+      <c r="T11" s="25">
         <v>2036</v>
       </c>
-      <c r="U10" s="25">
+      <c r="U11" s="25">
         <v>2037</v>
       </c>
-      <c r="V10" s="25">
+      <c r="V11" s="25">
         <v>2038</v>
       </c>
-      <c r="W10" s="25">
+      <c r="W11" s="25">
         <v>2039</v>
       </c>
-      <c r="X10" s="25">
+      <c r="X11" s="25">
         <v>2040</v>
       </c>
-      <c r="Y10" s="25">
+      <c r="Y11" s="25">
         <v>2041</v>
       </c>
-      <c r="Z10" s="25">
+      <c r="Z11" s="25">
         <v>2042</v>
       </c>
-      <c r="AA10" s="25">
+      <c r="AA11" s="25">
         <v>2043</v>
       </c>
-      <c r="AB10" s="25">
+      <c r="AB11" s="25">
         <v>2044</v>
       </c>
-      <c r="AC10" s="25">
+      <c r="AC11" s="25">
         <v>2045</v>
       </c>
-      <c r="AD10" s="25">
+      <c r="AD11" s="25">
         <v>2046</v>
       </c>
-      <c r="AE10" s="25">
+      <c r="AE11" s="25">
         <v>2047</v>
       </c>
-      <c r="AF10" s="25">
+      <c r="AF11" s="25">
         <v>2048</v>
       </c>
-      <c r="AG10" s="25">
+      <c r="AG11" s="25">
         <v>2049</v>
       </c>
-      <c r="AH10" s="25">
+      <c r="AH11" s="25">
         <v>2050</v>
       </c>
-      <c r="AI10" s="25">
+      <c r="AI11" s="25">
         <v>2051</v>
       </c>
-      <c r="AJ10" s="25">
+      <c r="AJ11" s="25">
         <v>2052</v>
       </c>
-      <c r="AK10" s="25">
+      <c r="AK11" s="25">
         <v>2053</v>
       </c>
-      <c r="AL10" s="25">
+      <c r="AL11" s="25">
         <v>2054</v>
       </c>
-      <c r="AM10" s="25">
+      <c r="AM11" s="25">
         <v>2055</v>
       </c>
-      <c r="AN10" s="25">
+      <c r="AN11" s="25">
         <v>2056</v>
       </c>
-      <c r="AO10" s="25">
+      <c r="AO11" s="25">
         <v>2057</v>
       </c>
-      <c r="AP10" s="25">
+      <c r="AP11" s="25">
         <v>2058</v>
       </c>
-      <c r="AQ10" s="25">
+      <c r="AQ11" s="25">
         <v>2059</v>
       </c>
-      <c r="AR10" s="25">
+      <c r="AR11" s="25">
         <v>2060</v>
-      </c>
-      <c r="AS10" s="15"/>
-      <c r="AT10" s="15"/>
-    </row>
-    <row r="11" spans="1:46" ht="16" x14ac:dyDescent="0.4">
-      <c r="A11" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="C11" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="H11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="I11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="J11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="K11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="L11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="M11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="N11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="O11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="P11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="R11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="S11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="T11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="U11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="V11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="W11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="X11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="Z11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AA11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AB11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AC11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AD11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AE11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AF11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AG11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AH11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AI11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AJ11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AK11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AL11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AM11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AN11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AO11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AP11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AQ11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AR11" s="19" t="s">
-        <v>15</v>
       </c>
       <c r="AS11" s="15"/>
       <c r="AT11" s="15"/>
     </row>
     <row r="12" spans="1:46" ht="16" x14ac:dyDescent="0.4">
       <c r="A12" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D12" s="17">
-        <v>0</v>
-      </c>
-      <c r="E12" s="17">
-        <v>0</v>
-      </c>
-      <c r="F12" s="17">
-        <v>0</v>
-      </c>
-      <c r="G12" s="17">
-        <v>0</v>
-      </c>
-      <c r="H12" s="17">
-        <v>0</v>
-      </c>
-      <c r="I12" s="17">
-        <v>0</v>
-      </c>
-      <c r="J12" s="17">
-        <v>0</v>
-      </c>
-      <c r="K12" s="17">
-        <v>0</v>
-      </c>
-      <c r="L12" s="17">
-        <v>0</v>
-      </c>
-      <c r="M12" s="17">
-        <v>0</v>
-      </c>
-      <c r="N12" s="17">
-        <v>0</v>
-      </c>
-      <c r="O12" s="17">
-        <v>0</v>
-      </c>
-      <c r="P12" s="17">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="17">
-        <v>0</v>
-      </c>
-      <c r="R12" s="17">
-        <v>0</v>
-      </c>
-      <c r="S12" s="17">
-        <v>0</v>
-      </c>
-      <c r="T12" s="17">
-        <v>0</v>
-      </c>
-      <c r="U12" s="17">
-        <v>0</v>
-      </c>
-      <c r="V12" s="17">
-        <v>0</v>
-      </c>
-      <c r="W12" s="17">
-        <v>0</v>
-      </c>
-      <c r="X12" s="17">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="17">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AA12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AB12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AC12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AD12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AE12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AF12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AG12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AH12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AI12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AJ12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AK12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AL12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AM12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AN12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AO12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AP12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AQ12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AR12" s="17">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="J12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="K12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="L12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="M12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="N12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="O12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="P12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="R12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="S12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="T12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="U12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="V12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="W12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="X12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AF12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AI12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AJ12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AL12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AN12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AO12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AP12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AR12" s="19" t="s">
+        <v>15</v>
       </c>
       <c r="AS12" s="15"/>
       <c r="AT12" s="15"/>
     </row>
     <row r="13" spans="1:46" ht="16" x14ac:dyDescent="0.4">
-      <c r="A13" s="23"/>
-      <c r="B13" s="23"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="21"/>
-      <c r="K13" s="21"/>
-      <c r="L13" s="21"/>
-      <c r="M13" s="21"/>
-      <c r="N13" s="21"/>
-      <c r="O13" s="21"/>
-      <c r="P13" s="21"/>
-      <c r="Q13" s="21"/>
-      <c r="R13" s="21"/>
-      <c r="S13" s="21"/>
-      <c r="T13" s="21"/>
-      <c r="U13" s="21"/>
-      <c r="V13" s="21"/>
-      <c r="W13" s="21"/>
-      <c r="X13" s="21"/>
-      <c r="Y13" s="21"/>
-      <c r="Z13" s="21"/>
-      <c r="AA13" s="21"/>
-      <c r="AB13" s="21"/>
-      <c r="AC13" s="21"/>
-      <c r="AD13" s="21"/>
-      <c r="AE13" s="21"/>
-      <c r="AF13" s="21"/>
-      <c r="AG13" s="21"/>
-      <c r="AH13" s="21"/>
-      <c r="AI13" s="21"/>
-      <c r="AJ13" s="21"/>
-      <c r="AK13" s="21"/>
-      <c r="AL13" s="21"/>
-      <c r="AM13" s="21"/>
-      <c r="AN13" s="21"/>
-      <c r="AO13" s="21"/>
-      <c r="AP13" s="21"/>
-      <c r="AQ13" s="21"/>
-      <c r="AR13" s="21"/>
+      <c r="A13" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="17">
+        <v>0</v>
+      </c>
+      <c r="E13" s="17">
+        <v>0</v>
+      </c>
+      <c r="F13" s="17">
+        <v>0</v>
+      </c>
+      <c r="G13" s="17">
+        <v>0</v>
+      </c>
+      <c r="H13" s="17">
+        <v>0</v>
+      </c>
+      <c r="I13" s="17">
+        <v>0</v>
+      </c>
+      <c r="J13" s="17">
+        <v>0</v>
+      </c>
+      <c r="K13" s="17">
+        <v>0</v>
+      </c>
+      <c r="L13" s="17">
+        <v>0</v>
+      </c>
+      <c r="M13" s="17">
+        <v>0</v>
+      </c>
+      <c r="N13" s="17">
+        <v>0</v>
+      </c>
+      <c r="O13" s="17">
+        <v>0</v>
+      </c>
+      <c r="P13" s="17">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="17">
+        <v>0</v>
+      </c>
+      <c r="R13" s="17">
+        <v>0</v>
+      </c>
+      <c r="S13" s="17">
+        <v>0</v>
+      </c>
+      <c r="T13" s="17">
+        <v>0</v>
+      </c>
+      <c r="U13" s="17">
+        <v>0</v>
+      </c>
+      <c r="V13" s="17">
+        <v>0</v>
+      </c>
+      <c r="W13" s="17">
+        <v>0</v>
+      </c>
+      <c r="X13" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AM13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AN13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AP13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AR13" s="17">
+        <v>0</v>
+      </c>
       <c r="AS13" s="15"/>
       <c r="AT13" s="15"/>
     </row>
     <row r="14" spans="1:46" ht="16" x14ac:dyDescent="0.4">
-      <c r="A14" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="11">
-        <v>2020</v>
-      </c>
-      <c r="E14" s="11">
-        <v>2021</v>
-      </c>
-      <c r="F14" s="11">
-        <v>2022</v>
-      </c>
-      <c r="G14" s="11">
-        <v>2023</v>
-      </c>
-      <c r="H14" s="11">
-        <v>2024</v>
-      </c>
-      <c r="I14" s="11">
-        <v>2025</v>
-      </c>
-      <c r="J14" s="11">
-        <v>2026</v>
-      </c>
-      <c r="K14" s="11">
-        <v>2027</v>
-      </c>
-      <c r="L14" s="11">
-        <v>2028</v>
-      </c>
-      <c r="M14" s="11">
-        <v>2029</v>
-      </c>
-      <c r="N14" s="11">
-        <v>2030</v>
-      </c>
-      <c r="O14" s="11">
-        <v>2031</v>
-      </c>
-      <c r="P14" s="11">
-        <v>2032</v>
-      </c>
-      <c r="Q14" s="11">
-        <v>2033</v>
-      </c>
-      <c r="R14" s="11">
-        <v>2034</v>
-      </c>
-      <c r="S14" s="11">
-        <v>2035</v>
-      </c>
-      <c r="T14" s="11">
-        <v>2036</v>
-      </c>
-      <c r="U14" s="11">
-        <v>2037</v>
-      </c>
-      <c r="V14" s="11">
-        <v>2038</v>
-      </c>
-      <c r="W14" s="11">
-        <v>2039</v>
-      </c>
-      <c r="X14" s="11">
-        <v>2040</v>
-      </c>
-      <c r="Y14" s="11">
-        <v>2041</v>
-      </c>
-      <c r="Z14" s="11">
-        <v>2042</v>
-      </c>
-      <c r="AA14" s="11">
-        <v>2043</v>
-      </c>
-      <c r="AB14" s="11">
-        <v>2044</v>
-      </c>
-      <c r="AC14" s="11">
-        <v>2045</v>
-      </c>
-      <c r="AD14" s="11">
-        <v>2046</v>
-      </c>
-      <c r="AE14" s="11">
-        <v>2047</v>
-      </c>
-      <c r="AF14" s="11">
-        <v>2048</v>
-      </c>
-      <c r="AG14" s="11">
-        <v>2049</v>
-      </c>
-      <c r="AH14" s="11">
-        <v>2050</v>
-      </c>
-      <c r="AI14" s="11">
-        <v>2051</v>
-      </c>
-      <c r="AJ14" s="11">
-        <v>2052</v>
-      </c>
-      <c r="AK14" s="11">
-        <v>2053</v>
-      </c>
-      <c r="AL14" s="11">
-        <v>2054</v>
-      </c>
-      <c r="AM14" s="11">
-        <v>2055</v>
-      </c>
-      <c r="AN14" s="11">
-        <v>2056</v>
-      </c>
-      <c r="AO14" s="11">
-        <v>2057</v>
-      </c>
-      <c r="AP14" s="11">
-        <v>2058</v>
-      </c>
-      <c r="AQ14" s="11">
-        <v>2059</v>
-      </c>
-      <c r="AR14" s="11">
-        <v>2060</v>
-      </c>
+      <c r="A14" s="23"/>
+      <c r="B14" s="23"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="21"/>
+      <c r="L14" s="21"/>
+      <c r="M14" s="21"/>
+      <c r="N14" s="21"/>
+      <c r="O14" s="21"/>
+      <c r="P14" s="21"/>
+      <c r="Q14" s="21"/>
+      <c r="R14" s="21"/>
+      <c r="S14" s="21"/>
+      <c r="T14" s="21"/>
+      <c r="U14" s="21"/>
+      <c r="V14" s="21"/>
+      <c r="W14" s="21"/>
+      <c r="X14" s="21"/>
+      <c r="Y14" s="21"/>
+      <c r="Z14" s="21"/>
+      <c r="AA14" s="21"/>
+      <c r="AB14" s="21"/>
+      <c r="AC14" s="21"/>
+      <c r="AD14" s="21"/>
+      <c r="AE14" s="21"/>
+      <c r="AF14" s="21"/>
+      <c r="AG14" s="21"/>
+      <c r="AH14" s="21"/>
+      <c r="AI14" s="21"/>
+      <c r="AJ14" s="21"/>
+      <c r="AK14" s="21"/>
+      <c r="AL14" s="21"/>
+      <c r="AM14" s="21"/>
+      <c r="AN14" s="21"/>
+      <c r="AO14" s="21"/>
+      <c r="AP14" s="21"/>
+      <c r="AQ14" s="21"/>
+      <c r="AR14" s="21"/>
       <c r="AS14" s="15"/>
       <c r="AT14" s="15"/>
     </row>
     <row r="15" spans="1:46" ht="16" x14ac:dyDescent="0.4">
-      <c r="A15" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" s="17">
-        <v>0</v>
-      </c>
-      <c r="E15" s="17">
-        <v>0</v>
-      </c>
-      <c r="F15" s="17">
-        <v>0</v>
-      </c>
-      <c r="G15" s="17">
-        <v>0</v>
-      </c>
-      <c r="H15" s="17">
-        <v>0</v>
-      </c>
-      <c r="I15" s="17">
-        <v>0</v>
-      </c>
-      <c r="J15" s="17">
-        <v>0</v>
-      </c>
-      <c r="K15" s="17">
-        <v>0</v>
-      </c>
-      <c r="L15" s="17">
-        <v>0</v>
-      </c>
-      <c r="M15" s="17">
-        <v>0</v>
-      </c>
-      <c r="N15" s="17">
-        <v>0</v>
-      </c>
-      <c r="O15" s="17">
-        <v>0</v>
-      </c>
-      <c r="P15" s="17">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="17">
-        <v>0</v>
-      </c>
-      <c r="R15" s="17">
-        <v>0</v>
-      </c>
-      <c r="S15" s="17">
-        <v>0</v>
-      </c>
-      <c r="T15" s="17">
-        <v>0</v>
-      </c>
-      <c r="U15" s="17">
-        <v>0</v>
-      </c>
-      <c r="V15" s="17">
-        <v>0</v>
-      </c>
-      <c r="W15" s="17">
-        <v>0</v>
-      </c>
-      <c r="X15" s="17">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="17">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AC15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AD15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AE15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AF15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AG15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AH15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AI15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AJ15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AK15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AL15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AM15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AN15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AO15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AP15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AQ15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AR15" s="17">
-        <v>0</v>
+      <c r="A15" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="11">
+        <v>2020</v>
+      </c>
+      <c r="E15" s="11">
+        <v>2021</v>
+      </c>
+      <c r="F15" s="11">
+        <v>2022</v>
+      </c>
+      <c r="G15" s="11">
+        <v>2023</v>
+      </c>
+      <c r="H15" s="11">
+        <v>2024</v>
+      </c>
+      <c r="I15" s="11">
+        <v>2025</v>
+      </c>
+      <c r="J15" s="11">
+        <v>2026</v>
+      </c>
+      <c r="K15" s="11">
+        <v>2027</v>
+      </c>
+      <c r="L15" s="11">
+        <v>2028</v>
+      </c>
+      <c r="M15" s="11">
+        <v>2029</v>
+      </c>
+      <c r="N15" s="11">
+        <v>2030</v>
+      </c>
+      <c r="O15" s="11">
+        <v>2031</v>
+      </c>
+      <c r="P15" s="11">
+        <v>2032</v>
+      </c>
+      <c r="Q15" s="11">
+        <v>2033</v>
+      </c>
+      <c r="R15" s="11">
+        <v>2034</v>
+      </c>
+      <c r="S15" s="11">
+        <v>2035</v>
+      </c>
+      <c r="T15" s="11">
+        <v>2036</v>
+      </c>
+      <c r="U15" s="11">
+        <v>2037</v>
+      </c>
+      <c r="V15" s="11">
+        <v>2038</v>
+      </c>
+      <c r="W15" s="11">
+        <v>2039</v>
+      </c>
+      <c r="X15" s="11">
+        <v>2040</v>
+      </c>
+      <c r="Y15" s="11">
+        <v>2041</v>
+      </c>
+      <c r="Z15" s="11">
+        <v>2042</v>
+      </c>
+      <c r="AA15" s="11">
+        <v>2043</v>
+      </c>
+      <c r="AB15" s="11">
+        <v>2044</v>
+      </c>
+      <c r="AC15" s="11">
+        <v>2045</v>
+      </c>
+      <c r="AD15" s="11">
+        <v>2046</v>
+      </c>
+      <c r="AE15" s="11">
+        <v>2047</v>
+      </c>
+      <c r="AF15" s="11">
+        <v>2048</v>
+      </c>
+      <c r="AG15" s="11">
+        <v>2049</v>
+      </c>
+      <c r="AH15" s="11">
+        <v>2050</v>
+      </c>
+      <c r="AI15" s="11">
+        <v>2051</v>
+      </c>
+      <c r="AJ15" s="11">
+        <v>2052</v>
+      </c>
+      <c r="AK15" s="11">
+        <v>2053</v>
+      </c>
+      <c r="AL15" s="11">
+        <v>2054</v>
+      </c>
+      <c r="AM15" s="11">
+        <v>2055</v>
+      </c>
+      <c r="AN15" s="11">
+        <v>2056</v>
+      </c>
+      <c r="AO15" s="11">
+        <v>2057</v>
+      </c>
+      <c r="AP15" s="11">
+        <v>2058</v>
+      </c>
+      <c r="AQ15" s="11">
+        <v>2059</v>
+      </c>
+      <c r="AR15" s="11">
+        <v>2060</v>
       </c>
       <c r="AS15" s="15"/>
       <c r="AT15" s="15"/>
     </row>
     <row r="16" spans="1:46" ht="16" x14ac:dyDescent="0.4">
-      <c r="A16" s="15"/>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="15"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="15"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="15"/>
-      <c r="N16" s="15"/>
-      <c r="O16" s="15"/>
-      <c r="P16" s="15"/>
-      <c r="Q16" s="15"/>
-      <c r="R16" s="15"/>
-      <c r="S16" s="15"/>
-      <c r="T16" s="15"/>
-      <c r="U16" s="15"/>
-      <c r="V16" s="15"/>
-      <c r="W16" s="15"/>
-      <c r="X16" s="15"/>
-      <c r="Y16" s="15"/>
-      <c r="Z16" s="15"/>
-      <c r="AA16" s="15"/>
-      <c r="AB16" s="15"/>
-      <c r="AC16" s="15"/>
-      <c r="AD16" s="15"/>
-      <c r="AE16" s="15"/>
-      <c r="AF16" s="15"/>
-      <c r="AG16" s="15"/>
-      <c r="AH16" s="15"/>
-      <c r="AI16" s="15"/>
-      <c r="AJ16" s="16"/>
-      <c r="AK16" s="16"/>
-      <c r="AL16" s="15"/>
-      <c r="AM16" s="16"/>
-      <c r="AN16" s="16"/>
-      <c r="AO16" s="15"/>
-      <c r="AP16" s="15"/>
-      <c r="AQ16" s="15"/>
-      <c r="AR16" s="15"/>
-    </row>
-    <row r="17" spans="1:44" s="3" customFormat="1" ht="16" x14ac:dyDescent="0.35">
-      <c r="A17" s="10" t="s">
+      <c r="A16" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" s="17">
+        <v>0</v>
+      </c>
+      <c r="E16" s="17">
+        <v>0</v>
+      </c>
+      <c r="F16" s="17">
+        <v>0</v>
+      </c>
+      <c r="G16" s="17">
+        <v>0</v>
+      </c>
+      <c r="H16" s="17">
+        <v>0</v>
+      </c>
+      <c r="I16" s="17">
+        <v>0</v>
+      </c>
+      <c r="J16" s="17">
+        <v>0</v>
+      </c>
+      <c r="K16" s="17">
+        <v>0</v>
+      </c>
+      <c r="L16" s="17">
+        <v>0</v>
+      </c>
+      <c r="M16" s="17">
+        <v>0</v>
+      </c>
+      <c r="N16" s="17">
+        <v>0</v>
+      </c>
+      <c r="O16" s="17">
+        <v>0</v>
+      </c>
+      <c r="P16" s="17">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="17">
+        <v>0</v>
+      </c>
+      <c r="R16" s="17">
+        <v>0</v>
+      </c>
+      <c r="S16" s="17">
+        <v>0</v>
+      </c>
+      <c r="T16" s="17">
+        <v>0</v>
+      </c>
+      <c r="U16" s="17">
+        <v>0</v>
+      </c>
+      <c r="V16" s="17">
+        <v>0</v>
+      </c>
+      <c r="W16" s="17">
+        <v>0</v>
+      </c>
+      <c r="X16" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AF16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AG16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AH16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AI16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AJ16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AK16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AL16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AM16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AN16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AO16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AP16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AQ16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AR16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AS16" s="15"/>
+      <c r="AT16" s="15"/>
+    </row>
+    <row r="17" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A17" s="15"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="15"/>
+      <c r="M17" s="15"/>
+      <c r="N17" s="15"/>
+      <c r="O17" s="15"/>
+      <c r="P17" s="15"/>
+      <c r="Q17" s="15"/>
+      <c r="R17" s="15"/>
+      <c r="S17" s="15"/>
+      <c r="T17" s="15"/>
+      <c r="U17" s="15"/>
+      <c r="V17" s="15"/>
+      <c r="W17" s="15"/>
+      <c r="X17" s="15"/>
+      <c r="Y17" s="15"/>
+      <c r="Z17" s="15"/>
+      <c r="AA17" s="15"/>
+      <c r="AB17" s="15"/>
+      <c r="AC17" s="15"/>
+      <c r="AD17" s="15"/>
+      <c r="AE17" s="15"/>
+      <c r="AF17" s="15"/>
+      <c r="AG17" s="15"/>
+      <c r="AH17" s="15"/>
+      <c r="AI17" s="15"/>
+      <c r="AJ17" s="16"/>
+      <c r="AK17" s="16"/>
+      <c r="AL17" s="15"/>
+      <c r="AM17" s="16"/>
+      <c r="AN17" s="16"/>
+      <c r="AO17" s="15"/>
+      <c r="AP17" s="15"/>
+      <c r="AQ17" s="15"/>
+      <c r="AR17" s="15"/>
+    </row>
+    <row r="18" spans="1:44" s="3" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A18" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B18" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C18" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="12"/>
-      <c r="J17" s="12"/>
-      <c r="K17" s="12"/>
-      <c r="L17" s="12"/>
-      <c r="M17" s="12"/>
-      <c r="N17" s="12"/>
-      <c r="O17" s="12"/>
-      <c r="P17" s="12"/>
-      <c r="Q17" s="12"/>
-      <c r="R17" s="12"/>
-      <c r="S17" s="12"/>
-      <c r="T17" s="12"/>
-      <c r="U17" s="12"/>
-      <c r="V17" s="12"/>
-      <c r="W17" s="12"/>
-      <c r="X17" s="12"/>
-      <c r="Y17" s="12"/>
-      <c r="Z17" s="12"/>
-      <c r="AA17" s="12"/>
-      <c r="AB17" s="12"/>
-      <c r="AC17" s="12"/>
-      <c r="AD17" s="12"/>
-      <c r="AE17" s="12"/>
-      <c r="AF17" s="12"/>
-      <c r="AG17" s="12"/>
-      <c r="AH17" s="12"/>
-      <c r="AI17" s="12"/>
-      <c r="AJ17" s="12"/>
-      <c r="AK17" s="12"/>
-      <c r="AL17" s="12"/>
-      <c r="AM17" s="12"/>
-      <c r="AN17" s="12"/>
-      <c r="AO17" s="12"/>
-      <c r="AP17" s="12"/>
-      <c r="AQ17" s="12"/>
-      <c r="AR17" s="12"/>
-    </row>
-    <row r="18" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A18" s="13" t="s">
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="12"/>
+      <c r="M18" s="12"/>
+      <c r="N18" s="12"/>
+      <c r="O18" s="12"/>
+      <c r="P18" s="12"/>
+      <c r="Q18" s="12"/>
+      <c r="R18" s="12"/>
+      <c r="S18" s="12"/>
+      <c r="T18" s="12"/>
+      <c r="U18" s="12"/>
+      <c r="V18" s="12"/>
+      <c r="W18" s="12"/>
+      <c r="X18" s="12"/>
+      <c r="Y18" s="12"/>
+      <c r="Z18" s="12"/>
+      <c r="AA18" s="12"/>
+      <c r="AB18" s="12"/>
+      <c r="AC18" s="12"/>
+      <c r="AD18" s="12"/>
+      <c r="AE18" s="12"/>
+      <c r="AF18" s="12"/>
+      <c r="AG18" s="12"/>
+      <c r="AH18" s="12"/>
+      <c r="AI18" s="12"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="12"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+    </row>
+    <row r="19" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A19" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="14">
-        <v>0</v>
-      </c>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8"/>
-      <c r="L18" s="8"/>
-      <c r="M18" s="8"/>
-      <c r="N18" s="8"/>
-      <c r="O18" s="8"/>
-      <c r="P18" s="8"/>
-      <c r="Q18" s="8"/>
-      <c r="R18" s="8"/>
-      <c r="S18" s="8"/>
-      <c r="T18" s="8"/>
-      <c r="U18" s="8"/>
-      <c r="V18" s="15"/>
-      <c r="W18" s="15"/>
-      <c r="X18" s="15"/>
-      <c r="Y18" s="15"/>
-      <c r="Z18" s="15"/>
-      <c r="AA18" s="15"/>
-      <c r="AB18" s="15"/>
-      <c r="AC18" s="15"/>
-      <c r="AD18" s="15"/>
-      <c r="AE18" s="15"/>
-      <c r="AF18" s="15"/>
-      <c r="AG18" s="15"/>
-      <c r="AH18" s="15"/>
-      <c r="AI18" s="15"/>
-      <c r="AJ18" s="15"/>
-      <c r="AK18" s="15"/>
-      <c r="AL18" s="15"/>
-      <c r="AM18" s="16"/>
-      <c r="AN18" s="16"/>
-      <c r="AO18" s="15"/>
-      <c r="AP18" s="15"/>
-      <c r="AQ18" s="15"/>
-      <c r="AR18" s="15"/>
-    </row>
-    <row r="19" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="1"/>
+      <c r="C19" s="14">
+        <v>0</v>
+      </c>
       <c r="D19" s="8"/>
       <c r="E19" s="8"/>
       <c r="F19" s="8"/>
@@ -4297,15 +4075,9 @@
       <c r="AR19" s="15"/>
     </row>
     <row r="20" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A20" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>8</v>
-      </c>
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="1"/>
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="8"/>
@@ -4349,14 +4121,14 @@
       <c r="AR20" s="15"/>
     </row>
     <row r="21" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A21" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="17">
-        <v>0</v>
+      <c r="A21" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>8</v>
       </c>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
@@ -4368,7 +4140,7 @@
       <c r="K21" s="8"/>
       <c r="L21" s="8"/>
       <c r="M21" s="8"/>
-      <c r="N21" s="2"/>
+      <c r="N21" s="8"/>
       <c r="O21" s="8"/>
       <c r="P21" s="8"/>
       <c r="Q21" s="8"/>
@@ -4402,7 +4174,7 @@
     </row>
     <row r="22" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A22" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>6</v>
@@ -4454,7 +4226,7 @@
     </row>
     <row r="23" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A23" s="5" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>6</v>
@@ -4472,7 +4244,7 @@
       <c r="K23" s="8"/>
       <c r="L23" s="8"/>
       <c r="M23" s="8"/>
-      <c r="N23" s="8"/>
+      <c r="N23" s="2"/>
       <c r="O23" s="8"/>
       <c r="P23" s="8"/>
       <c r="Q23" s="8"/>
@@ -4504,62 +4276,68 @@
       <c r="AQ23" s="15"/>
       <c r="AR23" s="15"/>
     </row>
-    <row r="24" spans="1:44" ht="16" x14ac:dyDescent="0.35">
-      <c r="A24" s="20" t="s">
+    <row r="24" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A24" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="17">
+        <v>0</v>
+      </c>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="N24" s="8"/>
+      <c r="O24" s="8"/>
+      <c r="P24" s="8"/>
+      <c r="Q24" s="8"/>
+      <c r="R24" s="8"/>
+      <c r="S24" s="8"/>
+      <c r="T24" s="8"/>
+      <c r="U24" s="8"/>
+      <c r="V24" s="15"/>
+      <c r="W24" s="15"/>
+      <c r="X24" s="15"/>
+      <c r="Y24" s="15"/>
+      <c r="Z24" s="15"/>
+      <c r="AA24" s="15"/>
+      <c r="AB24" s="15"/>
+      <c r="AC24" s="15"/>
+      <c r="AD24" s="15"/>
+      <c r="AE24" s="15"/>
+      <c r="AF24" s="15"/>
+      <c r="AG24" s="15"/>
+      <c r="AH24" s="15"/>
+      <c r="AI24" s="15"/>
+      <c r="AJ24" s="15"/>
+      <c r="AK24" s="15"/>
+      <c r="AL24" s="15"/>
+      <c r="AM24" s="16"/>
+      <c r="AN24" s="16"/>
+      <c r="AO24" s="15"/>
+      <c r="AP24" s="15"/>
+      <c r="AQ24" s="15"/>
+      <c r="AR24" s="15"/>
+    </row>
+    <row r="25" spans="1:44" ht="16" x14ac:dyDescent="0.35">
+      <c r="A25" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C24" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A25" s="15"/>
-      <c r="B25" s="15"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="15"/>
-      <c r="I25" s="15"/>
-      <c r="J25" s="15"/>
-      <c r="K25" s="15"/>
-      <c r="L25" s="15"/>
-      <c r="M25" s="15"/>
-      <c r="N25" s="15"/>
-      <c r="O25" s="15"/>
-      <c r="P25" s="15"/>
-      <c r="Q25" s="15"/>
-      <c r="R25" s="15"/>
-      <c r="S25" s="15"/>
-      <c r="T25" s="15"/>
-      <c r="U25" s="15"/>
-      <c r="V25" s="15"/>
-      <c r="W25" s="15"/>
-      <c r="X25" s="15"/>
-      <c r="Y25" s="15"/>
-      <c r="Z25" s="15"/>
-      <c r="AA25" s="15"/>
-      <c r="AB25" s="15"/>
-      <c r="AC25" s="15"/>
-      <c r="AD25" s="15"/>
-      <c r="AE25" s="15"/>
-      <c r="AF25" s="15"/>
-      <c r="AG25" s="15"/>
-      <c r="AH25" s="15"/>
-      <c r="AI25" s="15"/>
-      <c r="AJ25" s="16"/>
-      <c r="AK25" s="16"/>
-      <c r="AL25" s="15"/>
-      <c r="AM25" s="16"/>
-      <c r="AN25" s="16"/>
-      <c r="AO25" s="15"/>
-      <c r="AP25" s="15"/>
-      <c r="AQ25" s="15"/>
-      <c r="AR25" s="15"/>
+      <c r="B25" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C25" s="14">
+        <v>0</v>
+      </c>
     </row>
     <row r="26" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A26" s="15"/>
@@ -4600,35 +4378,81 @@
       <c r="AJ26" s="16"/>
       <c r="AK26" s="16"/>
       <c r="AL26" s="15"/>
-      <c r="AM26" s="15"/>
-      <c r="AN26" s="15"/>
+      <c r="AM26" s="16"/>
+      <c r="AN26" s="16"/>
       <c r="AO26" s="15"/>
       <c r="AP26" s="15"/>
       <c r="AQ26" s="15"/>
       <c r="AR26" s="15"/>
     </row>
+    <row r="27" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A27" s="15"/>
+      <c r="B27" s="15"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="15"/>
+      <c r="J27" s="15"/>
+      <c r="K27" s="15"/>
+      <c r="L27" s="15"/>
+      <c r="M27" s="15"/>
+      <c r="N27" s="15"/>
+      <c r="O27" s="15"/>
+      <c r="P27" s="15"/>
+      <c r="Q27" s="15"/>
+      <c r="R27" s="15"/>
+      <c r="S27" s="15"/>
+      <c r="T27" s="15"/>
+      <c r="U27" s="15"/>
+      <c r="V27" s="15"/>
+      <c r="W27" s="15"/>
+      <c r="X27" s="15"/>
+      <c r="Y27" s="15"/>
+      <c r="Z27" s="15"/>
+      <c r="AA27" s="15"/>
+      <c r="AB27" s="15"/>
+      <c r="AC27" s="15"/>
+      <c r="AD27" s="15"/>
+      <c r="AE27" s="15"/>
+      <c r="AF27" s="15"/>
+      <c r="AG27" s="15"/>
+      <c r="AH27" s="15"/>
+      <c r="AI27" s="15"/>
+      <c r="AJ27" s="16"/>
+      <c r="AK27" s="16"/>
+      <c r="AL27" s="15"/>
+      <c r="AM27" s="15"/>
+      <c r="AN27" s="15"/>
+      <c r="AO27" s="15"/>
+      <c r="AP27" s="15"/>
+      <c r="AQ27" s="15"/>
+      <c r="AR27" s="15"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A11:A13">
-    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
+  <conditionalFormatting sqref="A12:A14">
+    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
       <formula>"increase debt"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B11">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
+  <conditionalFormatting sqref="B12">
+    <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
       <formula>"increase debt"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="8" priority="4" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B5:AJ5">
-    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
+  <conditionalFormatting sqref="B6:AJ6">
+    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
       <formula>"increase debt"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4639,7 +4463,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1923DA0E-602E-4263-A988-9246800451B4}">
   <sheetPr codeName="Hoja3"/>
-  <dimension ref="A1:AT120"/>
+  <dimension ref="A1:AT27"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="39.36328125" customWidth="1"/>
@@ -4855,15 +4679,13 @@
       <c r="AR4" s="15"/>
     </row>
     <row r="5" spans="1:46" ht="16" x14ac:dyDescent="0.4">
-      <c r="A5" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="B5" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>15</v>
-      </c>
+      <c r="A5" s="27" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="14"/>
       <c r="D5" s="8"/>
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
@@ -4907,14 +4729,14 @@
       <c r="AR5" s="15"/>
     </row>
     <row r="6" spans="1:46" ht="16" x14ac:dyDescent="0.4">
-      <c r="A6" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C6" s="17">
-        <v>0</v>
+      <c r="A6" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>15</v>
       </c>
       <c r="D6" s="8"/>
       <c r="E6" s="8"/>
@@ -4951,8 +4773,8 @@
       <c r="AJ6" s="16"/>
       <c r="AK6" s="16"/>
       <c r="AL6" s="15"/>
-      <c r="AM6" s="16"/>
-      <c r="AN6" s="16"/>
+      <c r="AM6" s="15"/>
+      <c r="AN6" s="15"/>
       <c r="AO6" s="15"/>
       <c r="AP6" s="15"/>
       <c r="AQ6" s="15"/>
@@ -4960,10 +4782,10 @@
     </row>
     <row r="7" spans="1:46" ht="16" x14ac:dyDescent="0.4">
       <c r="A7" s="13" t="s">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C7" s="17">
         <v>0</v>
@@ -5000,8 +4822,8 @@
       <c r="AG7" s="15"/>
       <c r="AH7" s="15"/>
       <c r="AI7" s="15"/>
-      <c r="AJ7" s="15"/>
-      <c r="AK7" s="15"/>
+      <c r="AJ7" s="16"/>
+      <c r="AK7" s="16"/>
       <c r="AL7" s="15"/>
       <c r="AM7" s="16"/>
       <c r="AN7" s="16"/>
@@ -5012,7 +4834,7 @@
     </row>
     <row r="8" spans="1:46" ht="16" x14ac:dyDescent="0.4">
       <c r="A8" s="13" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>2</v>
@@ -5063,9 +4885,15 @@
       <c r="AR8" s="15"/>
     </row>
     <row r="9" spans="1:46" ht="16" x14ac:dyDescent="0.4">
-      <c r="A9" s="8"/>
-      <c r="B9" s="1"/>
-      <c r="C9" s="21"/>
+      <c r="A9" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="17">
+        <v>0</v>
+      </c>
       <c r="D9" s="8"/>
       <c r="E9" s="8"/>
       <c r="F9" s="8"/>
@@ -5109,887 +4937,887 @@
       <c r="AR9" s="15"/>
     </row>
     <row r="10" spans="1:46" ht="16" x14ac:dyDescent="0.4">
-      <c r="A10" s="24" t="s">
+      <c r="A10" s="8"/>
+      <c r="B10" s="1"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+      <c r="L10" s="8"/>
+      <c r="M10" s="8"/>
+      <c r="N10" s="8"/>
+      <c r="O10" s="8"/>
+      <c r="P10" s="8"/>
+      <c r="Q10" s="8"/>
+      <c r="R10" s="8"/>
+      <c r="S10" s="15"/>
+      <c r="T10" s="15"/>
+      <c r="U10" s="15"/>
+      <c r="V10" s="15"/>
+      <c r="W10" s="15"/>
+      <c r="X10" s="15"/>
+      <c r="Y10" s="15"/>
+      <c r="Z10" s="15"/>
+      <c r="AA10" s="15"/>
+      <c r="AB10" s="15"/>
+      <c r="AC10" s="15"/>
+      <c r="AD10" s="15"/>
+      <c r="AE10" s="15"/>
+      <c r="AF10" s="15"/>
+      <c r="AG10" s="15"/>
+      <c r="AH10" s="15"/>
+      <c r="AI10" s="15"/>
+      <c r="AJ10" s="15"/>
+      <c r="AK10" s="15"/>
+      <c r="AL10" s="15"/>
+      <c r="AM10" s="16"/>
+      <c r="AN10" s="16"/>
+      <c r="AO10" s="15"/>
+      <c r="AP10" s="15"/>
+      <c r="AQ10" s="15"/>
+      <c r="AR10" s="15"/>
+    </row>
+    <row r="11" spans="1:46" ht="16" x14ac:dyDescent="0.4">
+      <c r="A11" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="24" t="s">
+      <c r="B11" s="24" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="24" t="s">
+      <c r="C11" s="24" t="s">
         <v>12</v>
       </c>
-      <c r="D10" s="25">
+      <c r="D11" s="25">
         <v>2020</v>
       </c>
-      <c r="E10" s="25">
+      <c r="E11" s="25">
         <v>2021</v>
       </c>
-      <c r="F10" s="25">
+      <c r="F11" s="25">
         <v>2022</v>
       </c>
-      <c r="G10" s="25">
+      <c r="G11" s="25">
         <v>2023</v>
       </c>
-      <c r="H10" s="25">
+      <c r="H11" s="25">
         <v>2024</v>
       </c>
-      <c r="I10" s="25">
+      <c r="I11" s="25">
         <v>2025</v>
       </c>
-      <c r="J10" s="25">
+      <c r="J11" s="25">
         <v>2026</v>
       </c>
-      <c r="K10" s="25">
+      <c r="K11" s="25">
         <v>2027</v>
       </c>
-      <c r="L10" s="25">
+      <c r="L11" s="25">
         <v>2028</v>
       </c>
-      <c r="M10" s="25">
+      <c r="M11" s="25">
         <v>2029</v>
       </c>
-      <c r="N10" s="25">
+      <c r="N11" s="25">
         <v>2030</v>
       </c>
-      <c r="O10" s="25">
+      <c r="O11" s="25">
         <v>2031</v>
       </c>
-      <c r="P10" s="25">
+      <c r="P11" s="25">
         <v>2032</v>
       </c>
-      <c r="Q10" s="25">
+      <c r="Q11" s="25">
         <v>2033</v>
       </c>
-      <c r="R10" s="25">
+      <c r="R11" s="25">
         <v>2034</v>
       </c>
-      <c r="S10" s="25">
+      <c r="S11" s="25">
         <v>2035</v>
       </c>
-      <c r="T10" s="25">
+      <c r="T11" s="25">
         <v>2036</v>
       </c>
-      <c r="U10" s="25">
+      <c r="U11" s="25">
         <v>2037</v>
       </c>
-      <c r="V10" s="25">
+      <c r="V11" s="25">
         <v>2038</v>
       </c>
-      <c r="W10" s="25">
+      <c r="W11" s="25">
         <v>2039</v>
       </c>
-      <c r="X10" s="25">
+      <c r="X11" s="25">
         <v>2040</v>
       </c>
-      <c r="Y10" s="25">
+      <c r="Y11" s="25">
         <v>2041</v>
       </c>
-      <c r="Z10" s="25">
+      <c r="Z11" s="25">
         <v>2042</v>
       </c>
-      <c r="AA10" s="25">
+      <c r="AA11" s="25">
         <v>2043</v>
       </c>
-      <c r="AB10" s="25">
+      <c r="AB11" s="25">
         <v>2044</v>
       </c>
-      <c r="AC10" s="25">
+      <c r="AC11" s="25">
         <v>2045</v>
       </c>
-      <c r="AD10" s="25">
+      <c r="AD11" s="25">
         <v>2046</v>
       </c>
-      <c r="AE10" s="25">
+      <c r="AE11" s="25">
         <v>2047</v>
       </c>
-      <c r="AF10" s="25">
+      <c r="AF11" s="25">
         <v>2048</v>
       </c>
-      <c r="AG10" s="25">
+      <c r="AG11" s="25">
         <v>2049</v>
       </c>
-      <c r="AH10" s="25">
+      <c r="AH11" s="25">
         <v>2050</v>
       </c>
-      <c r="AI10" s="25">
+      <c r="AI11" s="25">
         <v>2051</v>
       </c>
-      <c r="AJ10" s="25">
+      <c r="AJ11" s="25">
         <v>2052</v>
       </c>
-      <c r="AK10" s="25">
+      <c r="AK11" s="25">
         <v>2053</v>
       </c>
-      <c r="AL10" s="25">
+      <c r="AL11" s="25">
         <v>2054</v>
       </c>
-      <c r="AM10" s="25">
+      <c r="AM11" s="25">
         <v>2055</v>
       </c>
-      <c r="AN10" s="25">
+      <c r="AN11" s="25">
         <v>2056</v>
       </c>
-      <c r="AO10" s="25">
+      <c r="AO11" s="25">
         <v>2057</v>
       </c>
-      <c r="AP10" s="25">
+      <c r="AP11" s="25">
         <v>2058</v>
       </c>
-      <c r="AQ10" s="25">
+      <c r="AQ11" s="25">
         <v>2059</v>
       </c>
-      <c r="AR10" s="25">
+      <c r="AR11" s="25">
         <v>2060</v>
-      </c>
-      <c r="AS10" s="15"/>
-      <c r="AT10" s="15"/>
-    </row>
-    <row r="11" spans="1:46" ht="16" x14ac:dyDescent="0.4">
-      <c r="A11" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="C11" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="E11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="G11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="H11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="I11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="J11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="K11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="L11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="M11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="N11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="O11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="P11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="R11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="S11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="T11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="U11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="V11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="W11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="X11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="Y11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="Z11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AA11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AB11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AC11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AD11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AE11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AF11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AG11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AH11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AI11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AJ11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AK11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AL11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AM11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AN11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AO11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AP11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AQ11" s="19" t="s">
-        <v>15</v>
-      </c>
-      <c r="AR11" s="19" t="s">
-        <v>15</v>
       </c>
       <c r="AS11" s="15"/>
       <c r="AT11" s="15"/>
     </row>
     <row r="12" spans="1:46" ht="16" x14ac:dyDescent="0.4">
       <c r="A12" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>10</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D12" s="17">
-        <v>0</v>
-      </c>
-      <c r="E12" s="17">
-        <v>0</v>
-      </c>
-      <c r="F12" s="17">
-        <v>0</v>
-      </c>
-      <c r="G12" s="17">
-        <v>0</v>
-      </c>
-      <c r="H12" s="17">
-        <v>0</v>
-      </c>
-      <c r="I12" s="17">
-        <v>0</v>
-      </c>
-      <c r="J12" s="17">
-        <v>0</v>
-      </c>
-      <c r="K12" s="17">
-        <v>0</v>
-      </c>
-      <c r="L12" s="17">
-        <v>0</v>
-      </c>
-      <c r="M12" s="17">
-        <v>0</v>
-      </c>
-      <c r="N12" s="17">
-        <v>0</v>
-      </c>
-      <c r="O12" s="17">
-        <v>0</v>
-      </c>
-      <c r="P12" s="17">
-        <v>0</v>
-      </c>
-      <c r="Q12" s="17">
-        <v>0</v>
-      </c>
-      <c r="R12" s="17">
-        <v>0</v>
-      </c>
-      <c r="S12" s="17">
-        <v>0</v>
-      </c>
-      <c r="T12" s="17">
-        <v>0</v>
-      </c>
-      <c r="U12" s="17">
-        <v>0</v>
-      </c>
-      <c r="V12" s="17">
-        <v>0</v>
-      </c>
-      <c r="W12" s="17">
-        <v>0</v>
-      </c>
-      <c r="X12" s="17">
-        <v>0</v>
-      </c>
-      <c r="Y12" s="17">
-        <v>0</v>
-      </c>
-      <c r="Z12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AA12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AB12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AC12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AD12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AE12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AF12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AG12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AH12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AI12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AJ12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AK12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AL12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AM12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AN12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AO12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AP12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AQ12" s="17">
-        <v>0</v>
-      </c>
-      <c r="AR12" s="17">
-        <v>0</v>
+        <v>4</v>
+      </c>
+      <c r="C12" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="E12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="J12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="K12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="L12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="M12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="N12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="O12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="P12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="R12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="S12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="T12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="U12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="V12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="W12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="X12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="Y12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AA12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AB12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AC12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AD12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AE12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AF12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AG12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AH12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AI12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AJ12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AK12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AL12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AM12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AN12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AO12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AP12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AQ12" s="19" t="s">
+        <v>15</v>
+      </c>
+      <c r="AR12" s="19" t="s">
+        <v>15</v>
       </c>
       <c r="AS12" s="15"/>
       <c r="AT12" s="15"/>
     </row>
     <row r="13" spans="1:46" ht="16" x14ac:dyDescent="0.4">
-      <c r="A13" s="23"/>
-      <c r="B13" s="23"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="21"/>
-      <c r="E13" s="21"/>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="21"/>
-      <c r="K13" s="21"/>
-      <c r="L13" s="21"/>
-      <c r="M13" s="21"/>
-      <c r="N13" s="21"/>
-      <c r="O13" s="21"/>
-      <c r="P13" s="21"/>
-      <c r="Q13" s="21"/>
-      <c r="R13" s="21"/>
-      <c r="S13" s="21"/>
-      <c r="T13" s="21"/>
-      <c r="U13" s="21"/>
-      <c r="V13" s="21"/>
-      <c r="W13" s="21"/>
-      <c r="X13" s="21"/>
-      <c r="Y13" s="21"/>
-      <c r="Z13" s="21"/>
-      <c r="AA13" s="21"/>
-      <c r="AB13" s="21"/>
-      <c r="AC13" s="21"/>
-      <c r="AD13" s="21"/>
-      <c r="AE13" s="21"/>
-      <c r="AF13" s="21"/>
-      <c r="AG13" s="21"/>
-      <c r="AH13" s="21"/>
-      <c r="AI13" s="21"/>
-      <c r="AJ13" s="21"/>
-      <c r="AK13" s="21"/>
-      <c r="AL13" s="21"/>
-      <c r="AM13" s="21"/>
-      <c r="AN13" s="21"/>
-      <c r="AO13" s="21"/>
-      <c r="AP13" s="21"/>
-      <c r="AQ13" s="21"/>
-      <c r="AR13" s="21"/>
+      <c r="A13" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>10</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D13" s="17">
+        <v>0</v>
+      </c>
+      <c r="E13" s="17">
+        <v>0</v>
+      </c>
+      <c r="F13" s="17">
+        <v>0</v>
+      </c>
+      <c r="G13" s="17">
+        <v>0</v>
+      </c>
+      <c r="H13" s="17">
+        <v>0</v>
+      </c>
+      <c r="I13" s="17">
+        <v>0</v>
+      </c>
+      <c r="J13" s="17">
+        <v>0</v>
+      </c>
+      <c r="K13" s="17">
+        <v>0</v>
+      </c>
+      <c r="L13" s="17">
+        <v>0</v>
+      </c>
+      <c r="M13" s="17">
+        <v>0</v>
+      </c>
+      <c r="N13" s="17">
+        <v>0</v>
+      </c>
+      <c r="O13" s="17">
+        <v>0</v>
+      </c>
+      <c r="P13" s="17">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="17">
+        <v>0</v>
+      </c>
+      <c r="R13" s="17">
+        <v>0</v>
+      </c>
+      <c r="S13" s="17">
+        <v>0</v>
+      </c>
+      <c r="T13" s="17">
+        <v>0</v>
+      </c>
+      <c r="U13" s="17">
+        <v>0</v>
+      </c>
+      <c r="V13" s="17">
+        <v>0</v>
+      </c>
+      <c r="W13" s="17">
+        <v>0</v>
+      </c>
+      <c r="X13" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AM13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AN13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AP13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="17">
+        <v>0</v>
+      </c>
+      <c r="AR13" s="17">
+        <v>0</v>
+      </c>
       <c r="AS13" s="15"/>
       <c r="AT13" s="15"/>
     </row>
     <row r="14" spans="1:46" ht="16" x14ac:dyDescent="0.4">
-      <c r="A14" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="B14" s="26" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="D14" s="11">
-        <v>2020</v>
-      </c>
-      <c r="E14" s="11">
-        <v>2021</v>
-      </c>
-      <c r="F14" s="11">
-        <v>2022</v>
-      </c>
-      <c r="G14" s="11">
-        <v>2023</v>
-      </c>
-      <c r="H14" s="11">
-        <v>2024</v>
-      </c>
-      <c r="I14" s="11">
-        <v>2025</v>
-      </c>
-      <c r="J14" s="11">
-        <v>2026</v>
-      </c>
-      <c r="K14" s="11">
-        <v>2027</v>
-      </c>
-      <c r="L14" s="11">
-        <v>2028</v>
-      </c>
-      <c r="M14" s="11">
-        <v>2029</v>
-      </c>
-      <c r="N14" s="11">
-        <v>2030</v>
-      </c>
-      <c r="O14" s="11">
-        <v>2031</v>
-      </c>
-      <c r="P14" s="11">
-        <v>2032</v>
-      </c>
-      <c r="Q14" s="11">
-        <v>2033</v>
-      </c>
-      <c r="R14" s="11">
-        <v>2034</v>
-      </c>
-      <c r="S14" s="11">
-        <v>2035</v>
-      </c>
-      <c r="T14" s="11">
-        <v>2036</v>
-      </c>
-      <c r="U14" s="11">
-        <v>2037</v>
-      </c>
-      <c r="V14" s="11">
-        <v>2038</v>
-      </c>
-      <c r="W14" s="11">
-        <v>2039</v>
-      </c>
-      <c r="X14" s="11">
-        <v>2040</v>
-      </c>
-      <c r="Y14" s="11">
-        <v>2041</v>
-      </c>
-      <c r="Z14" s="11">
-        <v>2042</v>
-      </c>
-      <c r="AA14" s="11">
-        <v>2043</v>
-      </c>
-      <c r="AB14" s="11">
-        <v>2044</v>
-      </c>
-      <c r="AC14" s="11">
-        <v>2045</v>
-      </c>
-      <c r="AD14" s="11">
-        <v>2046</v>
-      </c>
-      <c r="AE14" s="11">
-        <v>2047</v>
-      </c>
-      <c r="AF14" s="11">
-        <v>2048</v>
-      </c>
-      <c r="AG14" s="11">
-        <v>2049</v>
-      </c>
-      <c r="AH14" s="11">
-        <v>2050</v>
-      </c>
-      <c r="AI14" s="11">
-        <v>2051</v>
-      </c>
-      <c r="AJ14" s="11">
-        <v>2052</v>
-      </c>
-      <c r="AK14" s="11">
-        <v>2053</v>
-      </c>
-      <c r="AL14" s="11">
-        <v>2054</v>
-      </c>
-      <c r="AM14" s="11">
-        <v>2055</v>
-      </c>
-      <c r="AN14" s="11">
-        <v>2056</v>
-      </c>
-      <c r="AO14" s="11">
-        <v>2057</v>
-      </c>
-      <c r="AP14" s="11">
-        <v>2058</v>
-      </c>
-      <c r="AQ14" s="11">
-        <v>2059</v>
-      </c>
-      <c r="AR14" s="11">
-        <v>2060</v>
-      </c>
+      <c r="A14" s="23"/>
+      <c r="B14" s="23"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="21"/>
+      <c r="L14" s="21"/>
+      <c r="M14" s="21"/>
+      <c r="N14" s="21"/>
+      <c r="O14" s="21"/>
+      <c r="P14" s="21"/>
+      <c r="Q14" s="21"/>
+      <c r="R14" s="21"/>
+      <c r="S14" s="21"/>
+      <c r="T14" s="21"/>
+      <c r="U14" s="21"/>
+      <c r="V14" s="21"/>
+      <c r="W14" s="21"/>
+      <c r="X14" s="21"/>
+      <c r="Y14" s="21"/>
+      <c r="Z14" s="21"/>
+      <c r="AA14" s="21"/>
+      <c r="AB14" s="21"/>
+      <c r="AC14" s="21"/>
+      <c r="AD14" s="21"/>
+      <c r="AE14" s="21"/>
+      <c r="AF14" s="21"/>
+      <c r="AG14" s="21"/>
+      <c r="AH14" s="21"/>
+      <c r="AI14" s="21"/>
+      <c r="AJ14" s="21"/>
+      <c r="AK14" s="21"/>
+      <c r="AL14" s="21"/>
+      <c r="AM14" s="21"/>
+      <c r="AN14" s="21"/>
+      <c r="AO14" s="21"/>
+      <c r="AP14" s="21"/>
+      <c r="AQ14" s="21"/>
+      <c r="AR14" s="21"/>
       <c r="AS14" s="15"/>
       <c r="AT14" s="15"/>
     </row>
     <row r="15" spans="1:46" ht="16" x14ac:dyDescent="0.4">
-      <c r="A15" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="D15" s="17">
-        <v>0</v>
-      </c>
-      <c r="E15" s="17">
-        <v>0</v>
-      </c>
-      <c r="F15" s="17">
-        <v>0</v>
-      </c>
-      <c r="G15" s="17">
-        <v>0</v>
-      </c>
-      <c r="H15" s="17">
-        <v>0</v>
-      </c>
-      <c r="I15" s="17">
-        <v>0</v>
-      </c>
-      <c r="J15" s="17">
-        <v>0</v>
-      </c>
-      <c r="K15" s="17">
-        <v>0</v>
-      </c>
-      <c r="L15" s="17">
-        <v>0</v>
-      </c>
-      <c r="M15" s="17">
-        <v>0</v>
-      </c>
-      <c r="N15" s="17">
-        <v>0</v>
-      </c>
-      <c r="O15" s="17">
-        <v>0</v>
-      </c>
-      <c r="P15" s="17">
-        <v>0</v>
-      </c>
-      <c r="Q15" s="17">
-        <v>0</v>
-      </c>
-      <c r="R15" s="17">
-        <v>0</v>
-      </c>
-      <c r="S15" s="17">
-        <v>0</v>
-      </c>
-      <c r="T15" s="17">
-        <v>0</v>
-      </c>
-      <c r="U15" s="17">
-        <v>0</v>
-      </c>
-      <c r="V15" s="17">
-        <v>0</v>
-      </c>
-      <c r="W15" s="17">
-        <v>0</v>
-      </c>
-      <c r="X15" s="17">
-        <v>0</v>
-      </c>
-      <c r="Y15" s="17">
-        <v>0</v>
-      </c>
-      <c r="Z15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AA15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AB15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AC15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AD15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AE15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AF15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AG15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AH15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AI15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AJ15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AK15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AL15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AM15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AN15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AO15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AP15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AQ15" s="17">
-        <v>0</v>
-      </c>
-      <c r="AR15" s="17">
-        <v>0</v>
+      <c r="A15" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="26" t="s">
+        <v>11</v>
+      </c>
+      <c r="C15" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="D15" s="11">
+        <v>2020</v>
+      </c>
+      <c r="E15" s="11">
+        <v>2021</v>
+      </c>
+      <c r="F15" s="11">
+        <v>2022</v>
+      </c>
+      <c r="G15" s="11">
+        <v>2023</v>
+      </c>
+      <c r="H15" s="11">
+        <v>2024</v>
+      </c>
+      <c r="I15" s="11">
+        <v>2025</v>
+      </c>
+      <c r="J15" s="11">
+        <v>2026</v>
+      </c>
+      <c r="K15" s="11">
+        <v>2027</v>
+      </c>
+      <c r="L15" s="11">
+        <v>2028</v>
+      </c>
+      <c r="M15" s="11">
+        <v>2029</v>
+      </c>
+      <c r="N15" s="11">
+        <v>2030</v>
+      </c>
+      <c r="O15" s="11">
+        <v>2031</v>
+      </c>
+      <c r="P15" s="11">
+        <v>2032</v>
+      </c>
+      <c r="Q15" s="11">
+        <v>2033</v>
+      </c>
+      <c r="R15" s="11">
+        <v>2034</v>
+      </c>
+      <c r="S15" s="11">
+        <v>2035</v>
+      </c>
+      <c r="T15" s="11">
+        <v>2036</v>
+      </c>
+      <c r="U15" s="11">
+        <v>2037</v>
+      </c>
+      <c r="V15" s="11">
+        <v>2038</v>
+      </c>
+      <c r="W15" s="11">
+        <v>2039</v>
+      </c>
+      <c r="X15" s="11">
+        <v>2040</v>
+      </c>
+      <c r="Y15" s="11">
+        <v>2041</v>
+      </c>
+      <c r="Z15" s="11">
+        <v>2042</v>
+      </c>
+      <c r="AA15" s="11">
+        <v>2043</v>
+      </c>
+      <c r="AB15" s="11">
+        <v>2044</v>
+      </c>
+      <c r="AC15" s="11">
+        <v>2045</v>
+      </c>
+      <c r="AD15" s="11">
+        <v>2046</v>
+      </c>
+      <c r="AE15" s="11">
+        <v>2047</v>
+      </c>
+      <c r="AF15" s="11">
+        <v>2048</v>
+      </c>
+      <c r="AG15" s="11">
+        <v>2049</v>
+      </c>
+      <c r="AH15" s="11">
+        <v>2050</v>
+      </c>
+      <c r="AI15" s="11">
+        <v>2051</v>
+      </c>
+      <c r="AJ15" s="11">
+        <v>2052</v>
+      </c>
+      <c r="AK15" s="11">
+        <v>2053</v>
+      </c>
+      <c r="AL15" s="11">
+        <v>2054</v>
+      </c>
+      <c r="AM15" s="11">
+        <v>2055</v>
+      </c>
+      <c r="AN15" s="11">
+        <v>2056</v>
+      </c>
+      <c r="AO15" s="11">
+        <v>2057</v>
+      </c>
+      <c r="AP15" s="11">
+        <v>2058</v>
+      </c>
+      <c r="AQ15" s="11">
+        <v>2059</v>
+      </c>
+      <c r="AR15" s="11">
+        <v>2060</v>
       </c>
       <c r="AS15" s="15"/>
       <c r="AT15" s="15"/>
     </row>
     <row r="16" spans="1:46" ht="16" x14ac:dyDescent="0.4">
-      <c r="A16" s="15"/>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
-      <c r="F16" s="15"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="15"/>
-      <c r="J16" s="15"/>
-      <c r="K16" s="15"/>
-      <c r="L16" s="15"/>
-      <c r="M16" s="15"/>
-      <c r="N16" s="15"/>
-      <c r="O16" s="15"/>
-      <c r="P16" s="15"/>
-      <c r="Q16" s="15"/>
-      <c r="R16" s="15"/>
-      <c r="S16" s="15"/>
-      <c r="T16" s="15"/>
-      <c r="U16" s="15"/>
-      <c r="V16" s="15"/>
-      <c r="W16" s="15"/>
-      <c r="X16" s="15"/>
-      <c r="Y16" s="15"/>
-      <c r="Z16" s="15"/>
-      <c r="AA16" s="15"/>
-      <c r="AB16" s="15"/>
-      <c r="AC16" s="15"/>
-      <c r="AD16" s="15"/>
-      <c r="AE16" s="15"/>
-      <c r="AF16" s="15"/>
-      <c r="AG16" s="15"/>
-      <c r="AH16" s="15"/>
-      <c r="AI16" s="15"/>
-      <c r="AJ16" s="16"/>
-      <c r="AK16" s="16"/>
-      <c r="AL16" s="15"/>
-      <c r="AM16" s="16"/>
-      <c r="AN16" s="16"/>
-      <c r="AO16" s="15"/>
-      <c r="AP16" s="15"/>
-      <c r="AQ16" s="15"/>
-      <c r="AR16" s="15"/>
-    </row>
-    <row r="17" spans="1:44" s="3" customFormat="1" ht="16" x14ac:dyDescent="0.35">
-      <c r="A17" s="10" t="s">
+      <c r="A16" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="D16" s="17">
+        <v>0</v>
+      </c>
+      <c r="E16" s="17">
+        <v>0</v>
+      </c>
+      <c r="F16" s="17">
+        <v>0</v>
+      </c>
+      <c r="G16" s="17">
+        <v>0</v>
+      </c>
+      <c r="H16" s="17">
+        <v>0</v>
+      </c>
+      <c r="I16" s="17">
+        <v>0</v>
+      </c>
+      <c r="J16" s="17">
+        <v>0</v>
+      </c>
+      <c r="K16" s="17">
+        <v>0</v>
+      </c>
+      <c r="L16" s="17">
+        <v>0</v>
+      </c>
+      <c r="M16" s="17">
+        <v>0</v>
+      </c>
+      <c r="N16" s="17">
+        <v>0</v>
+      </c>
+      <c r="O16" s="17">
+        <v>0</v>
+      </c>
+      <c r="P16" s="17">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="17">
+        <v>0</v>
+      </c>
+      <c r="R16" s="17">
+        <v>0</v>
+      </c>
+      <c r="S16" s="17">
+        <v>0</v>
+      </c>
+      <c r="T16" s="17">
+        <v>0</v>
+      </c>
+      <c r="U16" s="17">
+        <v>0</v>
+      </c>
+      <c r="V16" s="17">
+        <v>0</v>
+      </c>
+      <c r="W16" s="17">
+        <v>0</v>
+      </c>
+      <c r="X16" s="17">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="17">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AF16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AG16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AH16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AI16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AJ16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AK16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AL16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AM16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AN16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AO16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AP16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AQ16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AR16" s="17">
+        <v>0</v>
+      </c>
+      <c r="AS16" s="15"/>
+      <c r="AT16" s="15"/>
+    </row>
+    <row r="17" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A17" s="15"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
+      <c r="L17" s="15"/>
+      <c r="M17" s="15"/>
+      <c r="N17" s="15"/>
+      <c r="O17" s="15"/>
+      <c r="P17" s="15"/>
+      <c r="Q17" s="15"/>
+      <c r="R17" s="15"/>
+      <c r="S17" s="15"/>
+      <c r="T17" s="15"/>
+      <c r="U17" s="15"/>
+      <c r="V17" s="15"/>
+      <c r="W17" s="15"/>
+      <c r="X17" s="15"/>
+      <c r="Y17" s="15"/>
+      <c r="Z17" s="15"/>
+      <c r="AA17" s="15"/>
+      <c r="AB17" s="15"/>
+      <c r="AC17" s="15"/>
+      <c r="AD17" s="15"/>
+      <c r="AE17" s="15"/>
+      <c r="AF17" s="15"/>
+      <c r="AG17" s="15"/>
+      <c r="AH17" s="15"/>
+      <c r="AI17" s="15"/>
+      <c r="AJ17" s="16"/>
+      <c r="AK17" s="16"/>
+      <c r="AL17" s="15"/>
+      <c r="AM17" s="16"/>
+      <c r="AN17" s="16"/>
+      <c r="AO17" s="15"/>
+      <c r="AP17" s="15"/>
+      <c r="AQ17" s="15"/>
+      <c r="AR17" s="15"/>
+    </row>
+    <row r="18" spans="1:44" s="3" customFormat="1" ht="16" x14ac:dyDescent="0.35">
+      <c r="A18" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B17" s="10" t="s">
+      <c r="B18" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C18" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="12"/>
-      <c r="J17" s="12"/>
-      <c r="K17" s="12"/>
-      <c r="L17" s="12"/>
-      <c r="M17" s="12"/>
-      <c r="N17" s="12"/>
-      <c r="O17" s="12"/>
-      <c r="P17" s="12"/>
-      <c r="Q17" s="12"/>
-      <c r="R17" s="12"/>
-      <c r="S17" s="12"/>
-      <c r="T17" s="12"/>
-      <c r="U17" s="12"/>
-      <c r="V17" s="12"/>
-      <c r="W17" s="12"/>
-      <c r="X17" s="12"/>
-      <c r="Y17" s="12"/>
-      <c r="Z17" s="12"/>
-      <c r="AA17" s="12"/>
-      <c r="AB17" s="12"/>
-      <c r="AC17" s="12"/>
-      <c r="AD17" s="12"/>
-      <c r="AE17" s="12"/>
-      <c r="AF17" s="12"/>
-      <c r="AG17" s="12"/>
-      <c r="AH17" s="12"/>
-      <c r="AI17" s="12"/>
-      <c r="AJ17" s="12"/>
-      <c r="AK17" s="12"/>
-      <c r="AL17" s="12"/>
-      <c r="AM17" s="12"/>
-      <c r="AN17" s="12"/>
-      <c r="AO17" s="12"/>
-      <c r="AP17" s="12"/>
-      <c r="AQ17" s="12"/>
-      <c r="AR17" s="12"/>
-    </row>
-    <row r="18" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A18" s="13" t="s">
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="12"/>
+      <c r="G18" s="12"/>
+      <c r="H18" s="12"/>
+      <c r="I18" s="12"/>
+      <c r="J18" s="12"/>
+      <c r="K18" s="12"/>
+      <c r="L18" s="12"/>
+      <c r="M18" s="12"/>
+      <c r="N18" s="12"/>
+      <c r="O18" s="12"/>
+      <c r="P18" s="12"/>
+      <c r="Q18" s="12"/>
+      <c r="R18" s="12"/>
+      <c r="S18" s="12"/>
+      <c r="T18" s="12"/>
+      <c r="U18" s="12"/>
+      <c r="V18" s="12"/>
+      <c r="W18" s="12"/>
+      <c r="X18" s="12"/>
+      <c r="Y18" s="12"/>
+      <c r="Z18" s="12"/>
+      <c r="AA18" s="12"/>
+      <c r="AB18" s="12"/>
+      <c r="AC18" s="12"/>
+      <c r="AD18" s="12"/>
+      <c r="AE18" s="12"/>
+      <c r="AF18" s="12"/>
+      <c r="AG18" s="12"/>
+      <c r="AH18" s="12"/>
+      <c r="AI18" s="12"/>
+      <c r="AJ18" s="12"/>
+      <c r="AK18" s="12"/>
+      <c r="AL18" s="12"/>
+      <c r="AM18" s="12"/>
+      <c r="AN18" s="12"/>
+      <c r="AO18" s="12"/>
+      <c r="AP18" s="12"/>
+      <c r="AQ18" s="12"/>
+      <c r="AR18" s="12"/>
+    </row>
+    <row r="19" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A19" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B19" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="14">
-        <v>0</v>
-      </c>
-      <c r="D18" s="8"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
-      <c r="I18" s="8"/>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8"/>
-      <c r="L18" s="8"/>
-      <c r="M18" s="8"/>
-      <c r="N18" s="8"/>
-      <c r="O18" s="8"/>
-      <c r="P18" s="8"/>
-      <c r="Q18" s="8"/>
-      <c r="R18" s="8"/>
-      <c r="S18" s="8"/>
-      <c r="T18" s="8"/>
-      <c r="U18" s="8"/>
-      <c r="V18" s="15"/>
-      <c r="W18" s="15"/>
-      <c r="X18" s="15"/>
-      <c r="Y18" s="15"/>
-      <c r="Z18" s="15"/>
-      <c r="AA18" s="15"/>
-      <c r="AB18" s="15"/>
-      <c r="AC18" s="15"/>
-      <c r="AD18" s="15"/>
-      <c r="AE18" s="15"/>
-      <c r="AF18" s="15"/>
-      <c r="AG18" s="15"/>
-      <c r="AH18" s="15"/>
-      <c r="AI18" s="15"/>
-      <c r="AJ18" s="15"/>
-      <c r="AK18" s="15"/>
-      <c r="AL18" s="15"/>
-      <c r="AM18" s="16"/>
-      <c r="AN18" s="16"/>
-      <c r="AO18" s="15"/>
-      <c r="AP18" s="15"/>
-      <c r="AQ18" s="15"/>
-      <c r="AR18" s="15"/>
-    </row>
-    <row r="19" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="1"/>
+      <c r="C19" s="14">
+        <v>0</v>
+      </c>
       <c r="D19" s="8"/>
       <c r="E19" s="8"/>
       <c r="F19" s="8"/>
@@ -6033,15 +5861,9 @@
       <c r="AR19" s="15"/>
     </row>
     <row r="20" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A20" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="B20" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>8</v>
-      </c>
+      <c r="A20" s="7"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="1"/>
       <c r="D20" s="8"/>
       <c r="E20" s="8"/>
       <c r="F20" s="8"/>
@@ -6085,14 +5907,14 @@
       <c r="AR20" s="15"/>
     </row>
     <row r="21" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A21" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C21" s="17">
-        <v>0</v>
+      <c r="A21" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="B21" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>8</v>
       </c>
       <c r="D21" s="8"/>
       <c r="E21" s="8"/>
@@ -6104,7 +5926,7 @@
       <c r="K21" s="8"/>
       <c r="L21" s="8"/>
       <c r="M21" s="8"/>
-      <c r="N21" s="2"/>
+      <c r="N21" s="8"/>
       <c r="O21" s="8"/>
       <c r="P21" s="8"/>
       <c r="Q21" s="8"/>
@@ -6138,7 +5960,7 @@
     </row>
     <row r="22" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A22" s="5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>6</v>
@@ -6190,7 +6012,7 @@
     </row>
     <row r="23" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A23" s="5" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>6</v>
@@ -6208,7 +6030,7 @@
       <c r="K23" s="8"/>
       <c r="L23" s="8"/>
       <c r="M23" s="8"/>
-      <c r="N23" s="8"/>
+      <c r="N23" s="2"/>
       <c r="O23" s="8"/>
       <c r="P23" s="8"/>
       <c r="Q23" s="8"/>
@@ -6240,62 +6062,68 @@
       <c r="AQ23" s="15"/>
       <c r="AR23" s="15"/>
     </row>
-    <row r="24" spans="1:44" ht="16" x14ac:dyDescent="0.35">
-      <c r="A24" s="20" t="s">
+    <row r="24" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A24" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="17">
+        <v>0</v>
+      </c>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="8"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="8"/>
+      <c r="I24" s="8"/>
+      <c r="J24" s="8"/>
+      <c r="K24" s="8"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="8"/>
+      <c r="N24" s="8"/>
+      <c r="O24" s="8"/>
+      <c r="P24" s="8"/>
+      <c r="Q24" s="8"/>
+      <c r="R24" s="8"/>
+      <c r="S24" s="8"/>
+      <c r="T24" s="8"/>
+      <c r="U24" s="8"/>
+      <c r="V24" s="15"/>
+      <c r="W24" s="15"/>
+      <c r="X24" s="15"/>
+      <c r="Y24" s="15"/>
+      <c r="Z24" s="15"/>
+      <c r="AA24" s="15"/>
+      <c r="AB24" s="15"/>
+      <c r="AC24" s="15"/>
+      <c r="AD24" s="15"/>
+      <c r="AE24" s="15"/>
+      <c r="AF24" s="15"/>
+      <c r="AG24" s="15"/>
+      <c r="AH24" s="15"/>
+      <c r="AI24" s="15"/>
+      <c r="AJ24" s="15"/>
+      <c r="AK24" s="15"/>
+      <c r="AL24" s="15"/>
+      <c r="AM24" s="16"/>
+      <c r="AN24" s="16"/>
+      <c r="AO24" s="15"/>
+      <c r="AP24" s="15"/>
+      <c r="AQ24" s="15"/>
+      <c r="AR24" s="15"/>
+    </row>
+    <row r="25" spans="1:44" ht="16" x14ac:dyDescent="0.35">
+      <c r="A25" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="B24" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="C24" s="14">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:44" ht="16" x14ac:dyDescent="0.4">
-      <c r="A25" s="15"/>
-      <c r="B25" s="15"/>
-      <c r="C25" s="15"/>
-      <c r="D25" s="15"/>
-      <c r="E25" s="15"/>
-      <c r="F25" s="15"/>
-      <c r="G25" s="15"/>
-      <c r="H25" s="15"/>
-      <c r="I25" s="15"/>
-      <c r="J25" s="15"/>
-      <c r="K25" s="15"/>
-      <c r="L25" s="15"/>
-      <c r="M25" s="15"/>
-      <c r="N25" s="15"/>
-      <c r="O25" s="15"/>
-      <c r="P25" s="15"/>
-      <c r="Q25" s="15"/>
-      <c r="R25" s="15"/>
-      <c r="S25" s="15"/>
-      <c r="T25" s="15"/>
-      <c r="U25" s="15"/>
-      <c r="V25" s="15"/>
-      <c r="W25" s="15"/>
-      <c r="X25" s="15"/>
-      <c r="Y25" s="15"/>
-      <c r="Z25" s="15"/>
-      <c r="AA25" s="15"/>
-      <c r="AB25" s="15"/>
-      <c r="AC25" s="15"/>
-      <c r="AD25" s="15"/>
-      <c r="AE25" s="15"/>
-      <c r="AF25" s="15"/>
-      <c r="AG25" s="15"/>
-      <c r="AH25" s="15"/>
-      <c r="AI25" s="15"/>
-      <c r="AJ25" s="16"/>
-      <c r="AK25" s="16"/>
-      <c r="AL25" s="15"/>
-      <c r="AM25" s="16"/>
-      <c r="AN25" s="16"/>
-      <c r="AO25" s="15"/>
-      <c r="AP25" s="15"/>
-      <c r="AQ25" s="15"/>
-      <c r="AR25" s="15"/>
+      <c r="B25" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C25" s="14">
+        <v>0</v>
+      </c>
     </row>
     <row r="26" spans="1:44" ht="16" x14ac:dyDescent="0.4">
       <c r="A26" s="15"/>
@@ -6336,123 +6164,81 @@
       <c r="AJ26" s="16"/>
       <c r="AK26" s="16"/>
       <c r="AL26" s="15"/>
-      <c r="AM26" s="15"/>
-      <c r="AN26" s="15"/>
+      <c r="AM26" s="16"/>
+      <c r="AN26" s="16"/>
       <c r="AO26" s="15"/>
       <c r="AP26" s="15"/>
       <c r="AQ26" s="15"/>
       <c r="AR26" s="15"/>
     </row>
-    <row r="33" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="34" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="35" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="36" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="37" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="38" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="39" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="40" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="41" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="42" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="43" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="44" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="45" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="46" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="47" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="48" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="49" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="50" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="51" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="52" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="53" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="54" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="55" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="56" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="57" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="58" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="59" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="60" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="61" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="62" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="63" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="64" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="65" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="66" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="67" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="68" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="69" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="70" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="71" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="72" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="73" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="74" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="75" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="76" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="77" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="78" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="79" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="80" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="81" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="82" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="83" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="84" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="85" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="86" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="87" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="88" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="89" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="90" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="91" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="92" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="93" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="94" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="95" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="96" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="97" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="98" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="99" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="100" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="101" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="102" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="103" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="104" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="105" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="106" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="107" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="108" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="109" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="110" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="111" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="112" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="113" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="114" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="115" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="116" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="117" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="118" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="119" customFormat="1" x14ac:dyDescent="0.35"/>
-    <row r="120" customFormat="1" x14ac:dyDescent="0.35"/>
+    <row r="27" spans="1:44" ht="16" x14ac:dyDescent="0.4">
+      <c r="A27" s="15"/>
+      <c r="B27" s="15"/>
+      <c r="C27" s="15"/>
+      <c r="D27" s="15"/>
+      <c r="E27" s="15"/>
+      <c r="F27" s="15"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="15"/>
+      <c r="I27" s="15"/>
+      <c r="J27" s="15"/>
+      <c r="K27" s="15"/>
+      <c r="L27" s="15"/>
+      <c r="M27" s="15"/>
+      <c r="N27" s="15"/>
+      <c r="O27" s="15"/>
+      <c r="P27" s="15"/>
+      <c r="Q27" s="15"/>
+      <c r="R27" s="15"/>
+      <c r="S27" s="15"/>
+      <c r="T27" s="15"/>
+      <c r="U27" s="15"/>
+      <c r="V27" s="15"/>
+      <c r="W27" s="15"/>
+      <c r="X27" s="15"/>
+      <c r="Y27" s="15"/>
+      <c r="Z27" s="15"/>
+      <c r="AA27" s="15"/>
+      <c r="AB27" s="15"/>
+      <c r="AC27" s="15"/>
+      <c r="AD27" s="15"/>
+      <c r="AE27" s="15"/>
+      <c r="AF27" s="15"/>
+      <c r="AG27" s="15"/>
+      <c r="AH27" s="15"/>
+      <c r="AI27" s="15"/>
+      <c r="AJ27" s="16"/>
+      <c r="AK27" s="16"/>
+      <c r="AL27" s="15"/>
+      <c r="AM27" s="15"/>
+      <c r="AN27" s="15"/>
+      <c r="AO27" s="15"/>
+      <c r="AP27" s="15"/>
+      <c r="AQ27" s="15"/>
+      <c r="AR27" s="15"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A11:A13">
-    <cfRule type="cellIs" dxfId="11" priority="1" operator="equal">
+  <conditionalFormatting sqref="A12:A14">
+    <cfRule type="cellIs" dxfId="5" priority="1" operator="equal">
       <formula>"increase debt"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="2" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="2" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B11">
-    <cfRule type="cellIs" dxfId="9" priority="3" operator="equal">
+  <conditionalFormatting sqref="B12">
+    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
       <formula>"increase debt"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="4" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B5:AJ5">
-    <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
+  <conditionalFormatting sqref="B6:AJ6">
+    <cfRule type="cellIs" dxfId="1" priority="5" operator="equal">
       <formula>"increase debt"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="6" operator="equal">
       <formula>"ok"</formula>
     </cfRule>
   </conditionalFormatting>
